--- a/examples/sequence/OUL/output/10_10/ObjectsInUpdatingLocationsExperiment.xlsx
+++ b/examples/sequence/OUL/output/10_10/ObjectsInUpdatingLocationsExperiment.xlsx
@@ -739,28 +739,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.70879120879121</v>
+        <v>28.41604350781781</v>
       </c>
       <c r="C4" t="n">
-        <v>71.29120879120879</v>
+        <v>71.5839564921822</v>
       </c>
       <c r="D4" t="n">
-        <v>48.53333333333333</v>
+        <v>49.03333333333333</v>
       </c>
       <c r="E4" t="n">
         <v>13.93333333333333</v>
       </c>
       <c r="F4" t="n">
-        <v>34.6</v>
+        <v>35.1</v>
       </c>
       <c r="G4" t="n">
-        <v>8.833656270609112</v>
+        <v>9.11505791341882</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03780241957014977</v>
+        <v>0.03875371463433631</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02234552655327681</v>
+        <v>0.02391943873250987</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -769,16 +769,16 @@
         <v>21</v>
       </c>
       <c r="L4" t="n">
-        <v>189.4</v>
+        <v>189.6333333333333</v>
       </c>
       <c r="M4" t="n">
-        <v>2.752751771572371</v>
+        <v>2.745594545443179</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05215127569424061</v>
+        <v>0.05096882334442601</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03293323923978757</v>
+        <v>0.03168634225842838</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -790,31 +790,31 @@
         <v>63.83333333333334</v>
       </c>
       <c r="S4" t="n">
-        <v>16.17455865862775</v>
+        <v>16.33454821035222</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02197648884121278</v>
+        <v>0.02228481254631886</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0112447047974432</v>
+        <v>0.01260553708988781</v>
       </c>
       <c r="V4" t="n">
-        <v>20.46666666666667</v>
+        <v>24.43333333333334</v>
       </c>
       <c r="W4" t="n">
         <v>30</v>
       </c>
       <c r="X4" t="n">
-        <v>497.5</v>
+        <v>497.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.283277637934058</v>
+        <v>7.461216436418219</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.04325155872930624</v>
+        <v>0.04502149578153387</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.02395428458970596</v>
+        <v>0.02500579418509531</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -823,19 +823,19 @@
         <v>28</v>
       </c>
       <c r="AD4" t="n">
-        <v>149.2666666666667</v>
+        <v>149.1333333333333</v>
       </c>
       <c r="AE4" t="n">
-        <v>43.55270590297801</v>
+        <v>43.75419158521147</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.02919383343716336</v>
+        <v>0.03030744001855246</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.01517455418220792</v>
+        <v>0.01528118378650789</v>
       </c>
       <c r="AH4" t="n">
-        <v>20.46666666666667</v>
+        <v>24.43333333333333</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
@@ -874,46 +874,46 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33.77952755905512</v>
+        <v>33.28197226502311</v>
       </c>
       <c r="C5" t="n">
-        <v>66.22047244094489</v>
+        <v>66.71802773497689</v>
       </c>
       <c r="D5" t="n">
-        <v>42.33333333333334</v>
+        <v>43.26666666666667</v>
       </c>
       <c r="E5" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="F5" t="n">
-        <v>28.03333333333333</v>
+        <v>28.86666666666667</v>
       </c>
       <c r="G5" t="n">
-        <v>9.217540046635872</v>
+        <v>7.420111428475106</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05282906397181442</v>
+        <v>0.05106225245498518</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03512244989904378</v>
+        <v>0.03114326920931529</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L5" t="n">
-        <v>148.8</v>
+        <v>149.7333333333333</v>
       </c>
       <c r="M5" t="n">
-        <v>2.078010039933694</v>
+        <v>1.830220592722069</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0657444614879131</v>
+        <v>0.06820773985351002</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06689156517029342</v>
+        <v>0.04705609944309475</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -925,52 +925,52 @@
         <v>39.86666666666667</v>
       </c>
       <c r="S5" t="n">
-        <v>22.30714294515296</v>
+        <v>21.33693502763817</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03490257425815973</v>
+        <v>0.03420860333408346</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02498456602983168</v>
+        <v>0.02332471918485918</v>
       </c>
       <c r="V5" t="n">
-        <v>7.8</v>
+        <v>13.26666666666667</v>
       </c>
       <c r="W5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X5" t="n">
-        <v>484.3666666666667</v>
+        <v>483.5666666666667</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.967756880554603</v>
+        <v>8.816201004596961</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03262660478162813</v>
+        <v>0.03354632545850827</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01954268905835545</v>
+        <v>0.02051357294101894</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.066666666666667</v>
+        <v>2.1</v>
       </c>
       <c r="AC5" t="n">
         <v>31</v>
       </c>
       <c r="AD5" t="n">
-        <v>226.9333333333333</v>
+        <v>226.8333333333333</v>
       </c>
       <c r="AE5" t="n">
-        <v>52.06042780636186</v>
+        <v>48.35263749240943</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0367919505135213</v>
+        <v>0.03719223148268208</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.01974297318136542</v>
+        <v>0.01939185001360677</v>
       </c>
       <c r="AH5" t="n">
-        <v>8.866666666666667</v>
+        <v>15.36666666666667</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
@@ -1009,64 +1009,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58.46720214190093</v>
+        <v>58.25242718446602</v>
       </c>
       <c r="C6" t="n">
-        <v>41.53279785809907</v>
+        <v>41.74757281553399</v>
       </c>
       <c r="D6" t="n">
-        <v>99.59999999999999</v>
+        <v>99.56666666666666</v>
       </c>
       <c r="E6" t="n">
-        <v>58.23333333333333</v>
+        <v>58</v>
       </c>
       <c r="F6" t="n">
-        <v>41.36666666666667</v>
+        <v>41.56666666666667</v>
       </c>
       <c r="G6" t="n">
-        <v>37.35420167750978</v>
+        <v>30.50983904880422</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07868942795363197</v>
+        <v>0.0711347201482154</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05686552228585619</v>
+        <v>0.04062458547643422</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L6" t="n">
-        <v>406.4333333333333</v>
+        <v>406.6666666666667</v>
       </c>
       <c r="M6" t="n">
-        <v>5.802631283257712</v>
+        <v>5.463423692511205</v>
       </c>
       <c r="N6" t="n">
-        <v>0.06155886180002684</v>
+        <v>0.05972441703717468</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04656302314221288</v>
+        <v>0.04381684195387708</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R6" t="n">
-        <v>97.53333333333333</v>
+        <v>97.46666666666667</v>
       </c>
       <c r="S6" t="n">
-        <v>23.96844690815665</v>
+        <v>19.23873160794989</v>
       </c>
       <c r="T6" t="n">
-        <v>0.08904350985713172</v>
+        <v>0.08210118513726589</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0666383486669003</v>
+        <v>0.06261664617854477</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1075,34 +1075,34 @@
         <v>59</v>
       </c>
       <c r="X6" t="n">
-        <v>259.5333333333334</v>
+        <v>259.4333333333333</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.789693441755377</v>
+        <v>7.116814843441896</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.05986919862366505</v>
+        <v>0.05940101433252509</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03573397682009249</v>
+        <v>0.0281550159729088</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AD6" t="n">
-        <v>136.2</v>
+        <v>136.3333333333333</v>
       </c>
       <c r="AE6" t="n">
-        <v>104.724865782253</v>
+        <v>90.94970341124552</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.09085295101762472</v>
+        <v>0.0819420516687292</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.04487523265986604</v>
+        <v>0.04045796926835576</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
@@ -1142,103 +1142,103 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>39.14835164835165</v>
+        <v>38.76860622462788</v>
       </c>
       <c r="C7" t="n">
-        <v>60.85164835164836</v>
+        <v>61.23139377537213</v>
       </c>
       <c r="D7" t="n">
-        <v>48.53333333333333</v>
+        <v>49.26666666666667</v>
       </c>
       <c r="E7" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="F7" t="n">
-        <v>29.53333333333333</v>
+        <v>30.16666666666667</v>
       </c>
       <c r="G7" t="n">
-        <v>19.17174649619919</v>
+        <v>12.22465419255271</v>
       </c>
       <c r="H7" t="n">
-        <v>0.043179777397304</v>
+        <v>0.02850837526640454</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0194971949528274</v>
+        <v>0.0110189106308758</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>17.33333333333333</v>
       </c>
       <c r="K7" t="n">
         <v>16</v>
       </c>
       <c r="L7" t="n">
-        <v>325.3666666666667</v>
+        <v>325.7666666666667</v>
       </c>
       <c r="M7" t="n">
-        <v>18.81000346193657</v>
+        <v>12.39856762180926</v>
       </c>
       <c r="N7" t="n">
-        <v>0.04874934318831001</v>
+        <v>0.03488445478477201</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02413734979582554</v>
+        <v>0.02279332812630178</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.066666666666667</v>
       </c>
       <c r="Q7" t="n">
         <v>24</v>
       </c>
       <c r="R7" t="n">
-        <v>241.8333333333333</v>
+        <v>241.8</v>
       </c>
       <c r="S7" t="n">
-        <v>15.05253055098181</v>
+        <v>9.357699216215419</v>
       </c>
       <c r="T7" t="n">
-        <v>0.05899844799343622</v>
+        <v>0.03754240792590188</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02971485008235042</v>
+        <v>0.02019899480361965</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X7" t="n">
-        <v>146.0666666666667</v>
+        <v>146.1333333333333</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.80559274959341</v>
+        <v>10.15280648992944</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.06388860325784985</v>
+        <v>0.05144222835648798</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.03933401285200054</v>
+        <v>0.03493572695870564</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AD7" t="n">
-        <v>186.4</v>
+        <v>186.2</v>
       </c>
       <c r="AE7" t="n">
-        <v>74.40143708913027</v>
+        <v>50.80743136844674</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.04929633450295684</v>
+        <v>0.03152025612203782</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.02093466715678027</v>
+        <v>0.01506786289751416</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>19.4</v>
       </c>
       <c r="AI7" t="n">
         <v>385</v>
@@ -1275,103 +1275,103 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33.00871348026653</v>
+        <v>32.67477203647417</v>
       </c>
       <c r="C8" t="n">
-        <v>66.99128651973348</v>
+        <v>67.32522796352583</v>
       </c>
       <c r="D8" t="n">
-        <v>65.03333333333333</v>
+        <v>65.8</v>
       </c>
       <c r="E8" t="n">
-        <v>21.46666666666667</v>
+        <v>21.5</v>
       </c>
       <c r="F8" t="n">
-        <v>43.56666666666667</v>
+        <v>44.3</v>
       </c>
       <c r="G8" t="n">
-        <v>20.60190122577029</v>
+        <v>14.30583199507248</v>
       </c>
       <c r="H8" t="n">
-        <v>0.08422041434897619</v>
+        <v>0.07503447717307293</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07986501935938374</v>
+        <v>0.04012418694738473</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L8" t="n">
-        <v>202.2</v>
+        <v>203.1666666666667</v>
       </c>
       <c r="M8" t="n">
-        <v>12.45464282246387</v>
+        <v>11.21049276084251</v>
       </c>
       <c r="N8" t="n">
-        <v>0.06992085597917447</v>
+        <v>0.06297580514663965</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04361477986224731</v>
+        <v>0.03903834573680114</v>
       </c>
       <c r="P8" t="n">
         <v>1.033333333333333</v>
       </c>
       <c r="Q8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R8" t="n">
-        <v>160.4666666666667</v>
+        <v>160.3333333333333</v>
       </c>
       <c r="S8" t="n">
-        <v>21.92629520452574</v>
+        <v>21.55333042991285</v>
       </c>
       <c r="T8" t="n">
-        <v>0.04292193815850289</v>
+        <v>0.04421764920553335</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02799832948841285</v>
+        <v>0.02868832384478188</v>
       </c>
       <c r="V8" t="n">
-        <v>2.066666666666667</v>
+        <v>3.3</v>
       </c>
       <c r="W8" t="n">
         <v>41</v>
       </c>
       <c r="X8" t="n">
-        <v>389.8</v>
+        <v>389.5666666666667</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.950416874547236</v>
+        <v>6.917921351952747</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.05269667272683074</v>
+        <v>0.05320128828869539</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03069917332740793</v>
+        <v>0.02995182284950404</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AD8" t="n">
-        <v>147.1333333333333</v>
+        <v>146.9333333333333</v>
       </c>
       <c r="AE8" t="n">
-        <v>76.52651634573888</v>
+        <v>65.70498867781943</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.05810275206651494</v>
+        <v>0.05598820270924582</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.03532382132992229</v>
+        <v>0.03234457614456454</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.1</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
@@ -1410,46 +1410,46 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51.6294227188082</v>
+        <v>50.3820224719101</v>
       </c>
       <c r="C9" t="n">
-        <v>48.37057728119181</v>
+        <v>49.61797752808988</v>
       </c>
       <c r="D9" t="n">
-        <v>71.59999999999999</v>
+        <v>74.16666666666667</v>
       </c>
       <c r="E9" t="n">
-        <v>36.96666666666667</v>
+        <v>37.36666666666667</v>
       </c>
       <c r="F9" t="n">
-        <v>34.63333333333333</v>
+        <v>36.8</v>
       </c>
       <c r="G9" t="n">
-        <v>26.15047448040621</v>
+        <v>23.03043516327395</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09536398803186352</v>
+        <v>0.08661034345313907</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06914059980941017</v>
+        <v>0.05054420746818879</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L9" t="n">
-        <v>290.6666666666667</v>
+        <v>291.5666666666667</v>
       </c>
       <c r="M9" t="n">
-        <v>13.76676008798966</v>
+        <v>12.42608455450283</v>
       </c>
       <c r="N9" t="n">
-        <v>0.07184030924598948</v>
+        <v>0.07098421613658502</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06039965164630027</v>
+        <v>0.0494146247593414</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1458,55 +1458,55 @@
         <v>37</v>
       </c>
       <c r="R9" t="n">
-        <v>174.2333333333333</v>
+        <v>174.4</v>
       </c>
       <c r="S9" t="n">
-        <v>14.57569944968436</v>
+        <v>13.84768916939993</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0570150607379345</v>
+        <v>0.05485175080714103</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03414486450704429</v>
+        <v>0.02958391521595194</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.033333333333333</v>
       </c>
       <c r="W9" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="X9" t="n">
-        <v>240.0666666666667</v>
+        <v>239.5666666666667</v>
       </c>
       <c r="Y9" t="n">
-        <v>11.45624184760565</v>
+        <v>10.9456254133326</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.05595882518436933</v>
+        <v>0.05411499473807776</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.02934416981525413</v>
+        <v>0.03320994655294109</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.033333333333333</v>
       </c>
       <c r="AC9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AD9" t="n">
-        <v>194.8</v>
+        <v>194.4666666666667</v>
       </c>
       <c r="AE9" t="n">
-        <v>89.58608890174166</v>
+        <v>78.07649942099597</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.07092499033152294</v>
+        <v>0.06925828875404044</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.04300112180758353</v>
+        <v>0.0383616387213771</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.066666666666667</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
@@ -1545,82 +1545,82 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>45.57026476578411</v>
+        <v>44.57711442786069</v>
       </c>
       <c r="C10" t="n">
-        <v>54.42973523421589</v>
+        <v>55.42288557213931</v>
       </c>
       <c r="D10" t="n">
-        <v>65.46666666666667</v>
+        <v>67</v>
       </c>
       <c r="E10" t="n">
-        <v>29.83333333333333</v>
+        <v>29.86666666666667</v>
       </c>
       <c r="F10" t="n">
-        <v>35.63333333333333</v>
+        <v>37.13333333333333</v>
       </c>
       <c r="G10" t="n">
-        <v>23.56490372100851</v>
+        <v>19.60884949483712</v>
       </c>
       <c r="H10" t="n">
-        <v>0.08390181562522703</v>
+        <v>0.08095823209996031</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04956360972029897</v>
+        <v>0.04069606683534495</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L10" t="n">
-        <v>257.5666666666667</v>
+        <v>258.3666666666667</v>
       </c>
       <c r="M10" t="n">
-        <v>13.00938374357196</v>
+        <v>12.83912072244898</v>
       </c>
       <c r="N10" t="n">
-        <v>0.07211537977028003</v>
+        <v>0.07437886852184357</v>
       </c>
       <c r="O10" t="n">
-        <v>0.03810826391813154</v>
+        <v>0.03706186556213666</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R10" t="n">
-        <v>236.3666666666667</v>
+        <v>235.9666666666667</v>
       </c>
       <c r="S10" t="n">
-        <v>8.463908018105837</v>
+        <v>7.7337463596504</v>
       </c>
       <c r="T10" t="n">
-        <v>0.06056019109366971</v>
+        <v>0.06215474536576777</v>
       </c>
       <c r="U10" t="n">
-        <v>0.03495454684119718</v>
+        <v>0.03532941267846368</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="X10" t="n">
-        <v>173.8666666666667</v>
+        <v>173.4333333333333</v>
       </c>
       <c r="Y10" t="n">
-        <v>11.19558975915072</v>
+        <v>11.64620564853304</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0518581807601378</v>
+        <v>0.05415105312776708</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.03141944552832156</v>
+        <v>0.03196085188101016</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1629,16 +1629,16 @@
         <v>57</v>
       </c>
       <c r="AD10" t="n">
-        <v>232.1666666666667</v>
+        <v>232.2333333333333</v>
       </c>
       <c r="AE10" t="n">
-        <v>89.15003460947517</v>
+        <v>84.17496535976069</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.07708971395202904</v>
+        <v>0.07754152040405377</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.0414709214530754</v>
+        <v>0.04154549318871825</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
@@ -1680,46 +1680,46 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>48.20582261340555</v>
+        <v>47.74834437086093</v>
       </c>
       <c r="C11" t="n">
-        <v>51.79417738659445</v>
+        <v>52.25165562913907</v>
       </c>
       <c r="D11" t="n">
-        <v>49.23333333333333</v>
+        <v>50.33333333333334</v>
       </c>
       <c r="E11" t="n">
-        <v>23.73333333333333</v>
+        <v>24.03333333333333</v>
       </c>
       <c r="F11" t="n">
-        <v>25.5</v>
+        <v>26.3</v>
       </c>
       <c r="G11" t="n">
-        <v>8.781178266361781</v>
+        <v>6.911781402653224</v>
       </c>
       <c r="H11" t="n">
-        <v>0.08973085257983622</v>
+        <v>0.07648147248739816</v>
       </c>
       <c r="I11" t="n">
-        <v>0.06111695709746109</v>
+        <v>0.04107974058082405</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L11" t="n">
-        <v>94.13333333333334</v>
+        <v>93.63333333333334</v>
       </c>
       <c r="M11" t="n">
-        <v>8.923262596439182</v>
+        <v>6.793419514674829</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0571567560034241</v>
+        <v>0.05282444457183992</v>
       </c>
       <c r="O11" t="n">
-        <v>0.04088195970050529</v>
+        <v>0.02870287352319791</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1728,55 +1728,55 @@
         <v>18</v>
       </c>
       <c r="R11" t="n">
-        <v>116.8</v>
+        <v>117.0333333333333</v>
       </c>
       <c r="S11" t="n">
-        <v>17.04518208662753</v>
+        <v>14.1319122500719</v>
       </c>
       <c r="T11" t="n">
-        <v>0.02737898174308058</v>
+        <v>0.02573576510586826</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01542860743619522</v>
+        <v>0.01500857214544262</v>
       </c>
       <c r="V11" t="n">
-        <v>8.466666666666667</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="X11" t="n">
-        <v>395.0666666666667</v>
+        <v>395.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.968346949071929</v>
+        <v>9.107343574169171</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.02368766831599472</v>
+        <v>0.02206665405907585</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.01167112553891426</v>
+        <v>0.01163072183296941</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>3.233333333333333</v>
       </c>
       <c r="AC11" t="n">
         <v>32</v>
       </c>
       <c r="AD11" t="n">
-        <v>293.8666666666667</v>
+        <v>293.8333333333333</v>
       </c>
       <c r="AE11" t="n">
-        <v>52.23124822410513</v>
+        <v>43.74271807645906</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.03076739052593724</v>
+        <v>0.02990634427623484</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.01611131235989161</v>
+        <v>0.0151890797435601</v>
       </c>
       <c r="AH11" t="n">
-        <v>9.5</v>
+        <v>15.43333333333333</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
@@ -1815,103 +1815,103 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>57.54789272030651</v>
+        <v>56.17977528089888</v>
       </c>
       <c r="C12" t="n">
-        <v>42.45210727969349</v>
+        <v>43.82022471910112</v>
       </c>
       <c r="D12" t="n">
-        <v>43.5</v>
+        <v>47.46666666666667</v>
       </c>
       <c r="E12" t="n">
-        <v>25.03333333333333</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="F12" t="n">
-        <v>18.46666666666667</v>
+        <v>20.8</v>
       </c>
       <c r="G12" t="n">
-        <v>23.00518421891147</v>
+        <v>17.9606388473767</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1099220588678329</v>
+        <v>0.0847991844293467</v>
       </c>
       <c r="I12" t="n">
-        <v>0.05816784803401289</v>
+        <v>0.04633821933021277</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="K12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="L12" t="n">
-        <v>235.9666666666667</v>
+        <v>236.4666666666667</v>
       </c>
       <c r="M12" t="n">
-        <v>25.87971112412398</v>
+        <v>13.29491990168371</v>
       </c>
       <c r="N12" t="n">
-        <v>0.05264237762081358</v>
+        <v>0.04130288963842497</v>
       </c>
       <c r="O12" t="n">
-        <v>0.04528943510489403</v>
+        <v>0.02755783280260614</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="R12" t="n">
-        <v>248.6</v>
+        <v>248.3666666666667</v>
       </c>
       <c r="S12" t="n">
-        <v>18.32165794619868</v>
+        <v>11.65830248576183</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1066173923493951</v>
+        <v>0.0866512979485273</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1343082398322076</v>
+        <v>0.06698315605512566</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="X12" t="n">
-        <v>173.2</v>
+        <v>173.6666666666667</v>
       </c>
       <c r="Y12" t="n">
-        <v>13.95598051142082</v>
+        <v>11.27258979899745</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.06900647646690912</v>
+        <v>0.05320569179161772</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.03797503771997094</v>
+        <v>0.0319206064773714</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD12" t="n">
-        <v>241.5</v>
+        <v>241.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>125.786951505014</v>
+        <v>88.80945200759604</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.09487235760350338</v>
+        <v>0.07708161605591726</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.0454434968938735</v>
+        <v>0.04047560484862356</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>5.266666666666667</v>
       </c>
       <c r="AI12" t="n">
         <v>385</v>
@@ -1948,28 +1948,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>37.34177215189874</v>
+        <v>37.24747474747475</v>
       </c>
       <c r="C13" t="n">
-        <v>62.65822784810127</v>
+        <v>62.75252525252526</v>
       </c>
       <c r="D13" t="n">
-        <v>26.33333333333333</v>
+        <v>26.4</v>
       </c>
       <c r="E13" t="n">
         <v>9.833333333333334</v>
       </c>
       <c r="F13" t="n">
-        <v>16.5</v>
+        <v>16.56666666666667</v>
       </c>
       <c r="G13" t="n">
-        <v>11.09375112647026</v>
+        <v>7.823838084660764</v>
       </c>
       <c r="H13" t="n">
-        <v>0.07016806212336142</v>
+        <v>0.05403856954704492</v>
       </c>
       <c r="I13" t="n">
-        <v>0.03978366421868686</v>
+        <v>0.02673556270574402</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1978,73 +1978,73 @@
         <v>14</v>
       </c>
       <c r="L13" t="n">
-        <v>128.7</v>
+        <v>127.9</v>
       </c>
       <c r="M13" t="n">
-        <v>23.46460339804755</v>
+        <v>9.244395468132865</v>
       </c>
       <c r="N13" t="n">
-        <v>0.06891375865693766</v>
+        <v>0.05171670373430524</v>
       </c>
       <c r="O13" t="n">
-        <v>0.06416833540831623</v>
+        <v>0.03279732800596135</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R13" t="n">
-        <v>136.6</v>
+        <v>138</v>
       </c>
       <c r="S13" t="n">
-        <v>24.53271671088015</v>
+        <v>14.35846054804455</v>
       </c>
       <c r="T13" t="n">
-        <v>0.03388289706201217</v>
+        <v>0.02477598638600842</v>
       </c>
       <c r="U13" t="n">
-        <v>0.02460808886587303</v>
+        <v>0.014620156956202</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>32.76666666666667</v>
       </c>
       <c r="W13" t="n">
         <v>17</v>
       </c>
       <c r="X13" t="n">
-        <v>340.1666666666667</v>
+        <v>340.0666666666667</v>
       </c>
       <c r="Y13" t="n">
-        <v>19.06562525616076</v>
+        <v>14.1650360552595</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.05093252850690665</v>
+        <v>0.04259126321602492</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.02582249053562497</v>
+        <v>0.02226017866170266</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>4.300000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AD13" t="n">
-        <v>293.5</v>
+        <v>293.9333333333333</v>
       </c>
       <c r="AE13" t="n">
-        <v>100.3835916785824</v>
+        <v>50.60514572196175</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.04569071378924472</v>
+        <v>0.03480593411318095</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.02421939831794462</v>
+        <v>0.01846510602333062</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>37.06666666666667</v>
       </c>
       <c r="AI13" t="n">
         <v>385</v>
@@ -2081,28 +2081,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>39.19885550786838</v>
+        <v>39.27813163481953</v>
       </c>
       <c r="C14" t="n">
-        <v>60.80114449213161</v>
+        <v>60.72186836518046</v>
       </c>
       <c r="D14" t="n">
-        <v>46.6</v>
+        <v>47.1</v>
       </c>
       <c r="E14" t="n">
-        <v>18.26666666666667</v>
+        <v>18.5</v>
       </c>
       <c r="F14" t="n">
-        <v>28.33333333333333</v>
+        <v>28.6</v>
       </c>
       <c r="G14" t="n">
-        <v>9.262576628207256</v>
+        <v>8.353106308608064</v>
       </c>
       <c r="H14" t="n">
-        <v>0.08586957769242134</v>
+        <v>0.08000805030643975</v>
       </c>
       <c r="I14" t="n">
-        <v>0.06228850772788278</v>
+        <v>0.04714123248051181</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2111,16 +2111,16 @@
         <v>27</v>
       </c>
       <c r="L14" t="n">
-        <v>128.1666666666667</v>
+        <v>128.4666666666667</v>
       </c>
       <c r="M14" t="n">
-        <v>11.51079299113708</v>
+        <v>9.510012405219769</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0650986335568251</v>
+        <v>0.05452633443763823</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0368357054533913</v>
+        <v>0.03213969145903223</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -2129,16 +2129,16 @@
         <v>31</v>
       </c>
       <c r="R14" t="n">
-        <v>161.3</v>
+        <v>161.3666666666667</v>
       </c>
       <c r="S14" t="n">
-        <v>12.17392258557904</v>
+        <v>10.25626304645566</v>
       </c>
       <c r="T14" t="n">
-        <v>0.07913943975436309</v>
+        <v>0.07093067635864665</v>
       </c>
       <c r="U14" t="n">
-        <v>0.052713926517786</v>
+        <v>0.0447772932274872</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -2147,16 +2147,16 @@
         <v>33</v>
       </c>
       <c r="X14" t="n">
-        <v>151.2</v>
+        <v>151.0666666666667</v>
       </c>
       <c r="Y14" t="n">
-        <v>25.92621603613405</v>
+        <v>21.24244656359901</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.04597939083356587</v>
+        <v>0.03892144199214302</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.02561563492036344</v>
+        <v>0.01961397452725233</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2165,16 +2165,16 @@
         <v>36</v>
       </c>
       <c r="AD14" t="n">
-        <v>459.1666666666667</v>
+        <v>459</v>
       </c>
       <c r="AE14" t="n">
-        <v>76.71969046018256</v>
+        <v>65.25201317076832</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.06698889641972952</v>
+        <v>0.05695388016902703</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.03318849059924078</v>
+        <v>0.02745207199065924</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
@@ -2214,64 +2214,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>59.20692798541477</v>
+        <v>59.03197925669835</v>
       </c>
       <c r="C15" t="n">
-        <v>40.79307201458523</v>
+        <v>40.96802074330164</v>
       </c>
       <c r="D15" t="n">
-        <v>73.13333333333334</v>
+        <v>77.13333333333334</v>
       </c>
       <c r="E15" t="n">
-        <v>43.3</v>
+        <v>45.53333333333333</v>
       </c>
       <c r="F15" t="n">
-        <v>29.83333333333333</v>
+        <v>31.6</v>
       </c>
       <c r="G15" t="n">
-        <v>16.97445066701129</v>
+        <v>10.47998730825784</v>
       </c>
       <c r="H15" t="n">
-        <v>0.05500591033262967</v>
+        <v>0.0386511709894649</v>
       </c>
       <c r="I15" t="n">
-        <v>0.02676725505241276</v>
+        <v>0.02044482045030442</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="K15" t="n">
         <v>29</v>
       </c>
       <c r="L15" t="n">
-        <v>219.2666666666667</v>
+        <v>219.1</v>
       </c>
       <c r="M15" t="n">
-        <v>37.34183169513335</v>
+        <v>16.51334672133804</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0550193817182185</v>
+        <v>0.04050450881493093</v>
       </c>
       <c r="O15" t="n">
-        <v>0.030641659498721</v>
+        <v>0.02181853739025754</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>4.233333333333333</v>
       </c>
       <c r="Q15" t="n">
         <v>36</v>
       </c>
       <c r="R15" t="n">
-        <v>300.6333333333333</v>
+        <v>300.8666666666667</v>
       </c>
       <c r="S15" t="n">
-        <v>11.83047718487175</v>
+        <v>7.305176390703725</v>
       </c>
       <c r="T15" t="n">
-        <v>0.05303233398182861</v>
+        <v>0.04112822113842939</v>
       </c>
       <c r="U15" t="n">
-        <v>0.02810148016266543</v>
+        <v>0.02298081326983512</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -2280,37 +2280,37 @@
         <v>23</v>
       </c>
       <c r="X15" t="n">
-        <v>133.6666666666667</v>
+        <v>133.4333333333333</v>
       </c>
       <c r="Y15" t="n">
-        <v>25.61136377313837</v>
+        <v>14.40069066003403</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.06687317549090781</v>
+        <v>0.05100810779274316</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.05243258741186739</v>
+        <v>0.02642005969078455</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>3.133333333333334</v>
       </c>
       <c r="AC15" t="n">
         <v>31</v>
       </c>
       <c r="AD15" t="n">
-        <v>245.8333333333333</v>
+        <v>246.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>105.6831745226452</v>
+        <v>58.84644755498928</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.05977974635044356</v>
+        <v>0.044819035132872</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.03031518535423028</v>
+        <v>0.02280607235212073</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>8.466666666666667</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
@@ -2349,28 +2349,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>52.45989304812835</v>
+        <v>53.36734693877551</v>
       </c>
       <c r="C16" t="n">
-        <v>47.54010695187166</v>
+        <v>46.63265306122449</v>
       </c>
       <c r="D16" t="n">
-        <v>62.33333333333334</v>
+        <v>65.33333333333333</v>
       </c>
       <c r="E16" t="n">
-        <v>32.7</v>
+        <v>34.86666666666667</v>
       </c>
       <c r="F16" t="n">
-        <v>29.63333333333333</v>
+        <v>30.46666666666667</v>
       </c>
       <c r="G16" t="n">
-        <v>11.80094700089187</v>
+        <v>9.618119396350309</v>
       </c>
       <c r="H16" t="n">
-        <v>0.08079078330058075</v>
+        <v>0.06599005377891633</v>
       </c>
       <c r="I16" t="n">
-        <v>0.05099823916040912</v>
+        <v>0.04373593290403664</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2379,73 +2379,73 @@
         <v>28</v>
       </c>
       <c r="L16" t="n">
-        <v>131.9333333333333</v>
+        <v>131.9</v>
       </c>
       <c r="M16" t="n">
-        <v>28.29706398601596</v>
+        <v>18.65601472966256</v>
       </c>
       <c r="N16" t="n">
-        <v>0.07526108624704363</v>
+        <v>0.06103167476085951</v>
       </c>
       <c r="O16" t="n">
-        <v>0.05819033821888512</v>
+        <v>0.03773641079735559</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.033333333333333</v>
       </c>
       <c r="Q16" t="n">
         <v>35</v>
       </c>
       <c r="R16" t="n">
-        <v>254.9</v>
+        <v>255.2</v>
       </c>
       <c r="S16" t="n">
-        <v>21.64620069964834</v>
+        <v>13.04686962093074</v>
       </c>
       <c r="T16" t="n">
-        <v>0.06596461744058348</v>
+        <v>0.04824177575598083</v>
       </c>
       <c r="U16" t="n">
-        <v>0.05225481343740922</v>
+        <v>0.03030212530004846</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="W16" t="n">
         <v>30</v>
       </c>
       <c r="X16" t="n">
-        <v>196.6</v>
+        <v>196.8333333333333</v>
       </c>
       <c r="Y16" t="n">
-        <v>28.50365127224923</v>
+        <v>21.13365424809857</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.0709985475481824</v>
+        <v>0.05626814078207799</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.04258693898275246</v>
+        <v>0.03246252527201503</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>3.133333333333334</v>
       </c>
       <c r="AC16" t="n">
         <v>39</v>
       </c>
       <c r="AD16" t="n">
-        <v>316.2</v>
+        <v>315.9666666666666</v>
       </c>
       <c r="AE16" t="n">
-        <v>101.6472847193863</v>
+        <v>70.60625309895886</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.07913798307546979</v>
+        <v>0.06292229890967066</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.04377128189097756</v>
+        <v>0.03331070778514078</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>6.266666666666667</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
@@ -2484,103 +2484,103 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>63.22766570605187</v>
+        <v>62.46418338108883</v>
       </c>
       <c r="C17" t="n">
-        <v>36.77233429394812</v>
+        <v>37.53581661891117</v>
       </c>
       <c r="D17" t="n">
-        <v>57.83333333333334</v>
+        <v>58.16666666666666</v>
       </c>
       <c r="E17" t="n">
-        <v>36.56666666666667</v>
+        <v>36.33333333333334</v>
       </c>
       <c r="F17" t="n">
-        <v>21.26666666666667</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="G17" t="n">
-        <v>14.71706923767336</v>
+        <v>12.39315450219687</v>
       </c>
       <c r="H17" t="n">
-        <v>0.09317810035566201</v>
+        <v>0.0834219858576507</v>
       </c>
       <c r="I17" t="n">
-        <v>0.06192488212311577</v>
+        <v>0.04887747009605674</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L17" t="n">
-        <v>138.2</v>
+        <v>137.6666666666667</v>
       </c>
       <c r="M17" t="n">
-        <v>31.10494560485136</v>
+        <v>17.0080198386603</v>
       </c>
       <c r="N17" t="n">
-        <v>0.07421985418156161</v>
+        <v>0.06838472286953116</v>
       </c>
       <c r="O17" t="n">
-        <v>0.09357811430392381</v>
+        <v>0.03615484461693345</v>
       </c>
       <c r="P17" t="n">
+        <v>1.066666666666667</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>42</v>
+      </c>
+      <c r="R17" t="n">
+        <v>250.3666666666667</v>
+      </c>
+      <c r="S17" t="n">
+        <v>11.41939452969241</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.04903918885571999</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.03859471523314185</v>
+      </c>
+      <c r="V17" t="n">
         <v>1.033333333333333</v>
       </c>
-      <c r="Q17" t="n">
-        <v>41</v>
-      </c>
-      <c r="R17" t="n">
-        <v>249.6666666666667</v>
-      </c>
-      <c r="S17" t="n">
-        <v>16.13722056091931</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.0619483275842651</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0.07782236096856834</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
       <c r="W17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="X17" t="n">
-        <v>201.3666666666667</v>
+        <v>201.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>33.02931678894257</v>
+        <v>20.71872361023632</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.06855794436177445</v>
+        <v>0.05715149718344378</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.0469004890682503</v>
+        <v>0.03710676598813715</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD17" t="n">
-        <v>310.2333333333333</v>
+        <v>310.4666666666666</v>
       </c>
       <c r="AE17" t="n">
-        <v>108.7705493484267</v>
+        <v>72.50912346773143</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.07766368152265191</v>
+        <v>0.06570094758921047</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.04283956051949089</v>
+        <v>0.03544347530187975</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.033333333333333</v>
+        <v>2.1</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
@@ -2619,103 +2619,103 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>40.80267558528428</v>
+        <v>39.79430379746835</v>
       </c>
       <c r="C18" t="n">
-        <v>59.19732441471572</v>
+        <v>60.20569620253164</v>
       </c>
       <c r="D18" t="n">
-        <v>79.73333333333333</v>
+        <v>84.26666666666667</v>
       </c>
       <c r="E18" t="n">
-        <v>32.53333333333333</v>
+        <v>33.53333333333333</v>
       </c>
       <c r="F18" t="n">
-        <v>47.2</v>
+        <v>50.73333333333333</v>
       </c>
       <c r="G18" t="n">
-        <v>12.74932450299061</v>
+        <v>9.052765012020487</v>
       </c>
       <c r="H18" t="n">
-        <v>0.06187069601957357</v>
+        <v>0.04702066379770407</v>
       </c>
       <c r="I18" t="n">
-        <v>0.03459372062929492</v>
+        <v>0.02727227729521155</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L18" t="n">
-        <v>167.6666666666667</v>
+        <v>164.6</v>
       </c>
       <c r="M18" t="n">
-        <v>35.27902441971082</v>
+        <v>12.69908823754159</v>
       </c>
       <c r="N18" t="n">
-        <v>0.07660445233464608</v>
+        <v>0.06652821725589009</v>
       </c>
       <c r="O18" t="n">
-        <v>0.05438199982484563</v>
+        <v>0.04471188712064508</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.033333333333333</v>
       </c>
       <c r="Q18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R18" t="n">
-        <v>223.2</v>
+        <v>227.7</v>
       </c>
       <c r="S18" t="n">
-        <v>25.51614033196738</v>
+        <v>13.87391730291934</v>
       </c>
       <c r="T18" t="n">
-        <v>0.05107604043931523</v>
+        <v>0.03218152821939096</v>
       </c>
       <c r="U18" t="n">
-        <v>0.02708311487405095</v>
+        <v>0.01706038629758763</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.266666666666667</v>
       </c>
       <c r="W18" t="n">
         <v>38</v>
       </c>
       <c r="X18" t="n">
-        <v>293.7333333333333</v>
+        <v>293.4</v>
       </c>
       <c r="Y18" t="n">
-        <v>33.59402573096613</v>
+        <v>13.23273080817782</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.07449796287246958</v>
+        <v>0.0591851013877364</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.06431412892480934</v>
+        <v>0.03674866373803452</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="AC18" t="n">
         <v>34</v>
       </c>
       <c r="AD18" t="n">
-        <v>212.5666666666667</v>
+        <v>214.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>162.3689954752477</v>
+        <v>60.43809763681872</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.06641325999918057</v>
+        <v>0.0454629079394745</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.03615293066059078</v>
+        <v>0.02580156593797123</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>14.4</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
@@ -2754,46 +2754,46 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>41.44196951934349</v>
+        <v>41.31701631701632</v>
       </c>
       <c r="C19" t="n">
-        <v>58.5580304806565</v>
+        <v>58.68298368298368</v>
       </c>
       <c r="D19" t="n">
-        <v>56.86666666666667</v>
+        <v>57.2</v>
       </c>
       <c r="E19" t="n">
-        <v>23.56666666666667</v>
+        <v>23.63333333333333</v>
       </c>
       <c r="F19" t="n">
-        <v>33.3</v>
+        <v>33.56666666666667</v>
       </c>
       <c r="G19" t="n">
-        <v>21.24541617394219</v>
+        <v>16.19516292074221</v>
       </c>
       <c r="H19" t="n">
-        <v>0.07647648074701223</v>
+        <v>0.06402007732748825</v>
       </c>
       <c r="I19" t="n">
-        <v>0.04811937813505125</v>
+        <v>0.03613004527763271</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L19" t="n">
-        <v>239</v>
+        <v>238.8</v>
       </c>
       <c r="M19" t="n">
-        <v>21.25778313072767</v>
+        <v>13.57083753526369</v>
       </c>
       <c r="N19" t="n">
-        <v>0.08461263130169749</v>
+        <v>0.07530781768042188</v>
       </c>
       <c r="O19" t="n">
-        <v>0.09974226883356195</v>
+        <v>0.04594742772098373</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -2802,34 +2802,34 @@
         <v>57</v>
       </c>
       <c r="R19" t="n">
-        <v>222.9</v>
+        <v>223.3666666666667</v>
       </c>
       <c r="S19" t="n">
-        <v>26.92235885473653</v>
+        <v>13.4165398479797</v>
       </c>
       <c r="T19" t="n">
-        <v>0.05777053208470579</v>
+        <v>0.04269350963509705</v>
       </c>
       <c r="U19" t="n">
-        <v>0.03624660566363398</v>
+        <v>0.02183174711424493</v>
       </c>
       <c r="V19" t="n">
-        <v>1.033333333333333</v>
+        <v>4.6</v>
       </c>
       <c r="W19" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="X19" t="n">
-        <v>207.8</v>
+        <v>208.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>21.68928007244893</v>
+        <v>14.146288069276</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.0874030338009579</v>
+        <v>0.0757451529627256</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.05789430357541971</v>
+        <v>0.04263171506383998</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -2838,19 +2838,19 @@
         <v>51</v>
       </c>
       <c r="AD19" t="n">
-        <v>229.8333333333333</v>
+        <v>229.4333333333333</v>
       </c>
       <c r="AE19" t="n">
-        <v>123.4494897556724</v>
+        <v>81.58016713179067</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.08755326535481683</v>
+        <v>0.07414033278342327</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.04561575038260213</v>
+        <v>0.03396446440003897</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.033333333333333</v>
+        <v>4.6</v>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
@@ -2889,64 +2889,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>40.42443064182194</v>
+        <v>40.81841432225064</v>
       </c>
       <c r="C20" t="n">
-        <v>59.57556935817804</v>
+        <v>59.18158567774936</v>
       </c>
       <c r="D20" t="n">
-        <v>64.40000000000001</v>
+        <v>65.16666666666667</v>
       </c>
       <c r="E20" t="n">
-        <v>26.03333333333333</v>
+        <v>26.6</v>
       </c>
       <c r="F20" t="n">
-        <v>38.36666666666667</v>
+        <v>38.56666666666667</v>
       </c>
       <c r="G20" t="n">
-        <v>18.43983153276418</v>
+        <v>13.13058797243733</v>
       </c>
       <c r="H20" t="n">
-        <v>0.05688710443751151</v>
+        <v>0.04225970342367017</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03252485151606713</v>
+        <v>0.02553706730883546</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>2.066666666666667</v>
       </c>
       <c r="K20" t="n">
         <v>27</v>
       </c>
       <c r="L20" t="n">
-        <v>255.8666666666667</v>
+        <v>256.7</v>
       </c>
       <c r="M20" t="n">
-        <v>36.0811195621954</v>
+        <v>17.21893542934405</v>
       </c>
       <c r="N20" t="n">
-        <v>0.07165048620624492</v>
+        <v>0.05157583952603732</v>
       </c>
       <c r="O20" t="n">
-        <v>0.04421505405214878</v>
+        <v>0.0306468040059864</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>5.366666666666667</v>
       </c>
       <c r="Q20" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R20" t="n">
-        <v>234.9333333333333</v>
+        <v>234.5333333333333</v>
       </c>
       <c r="S20" t="n">
-        <v>14.51780763474986</v>
+        <v>10.13823157196216</v>
       </c>
       <c r="T20" t="n">
-        <v>0.06208495849519936</v>
+        <v>0.0441037034051902</v>
       </c>
       <c r="U20" t="n">
-        <v>0.03276097240293422</v>
+        <v>0.01995226485998469</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2955,37 +2955,37 @@
         <v>27</v>
       </c>
       <c r="X20" t="n">
-        <v>201.1666666666667</v>
+        <v>200.8666666666667</v>
       </c>
       <c r="Y20" t="n">
-        <v>17.12022937990245</v>
+        <v>13.33167904035242</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.0726868322829862</v>
+        <v>0.05691681011095463</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.04244109746790747</v>
+        <v>0.03249791187132048</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>3.133333333333334</v>
       </c>
       <c r="AC20" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AD20" t="n">
-        <v>207.6333333333333</v>
+        <v>207.8</v>
       </c>
       <c r="AE20" t="n">
-        <v>97.85623046593777</v>
+        <v>63.21723519040792</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.06837352226493176</v>
+        <v>0.05094079755398848</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.03708712607522124</v>
+        <v>0.02649859803524468</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>10.56666666666667</v>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
@@ -3024,64 +3024,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>41.99134199134199</v>
+        <v>40.04065040650406</v>
       </c>
       <c r="C21" t="n">
-        <v>58.008658008658</v>
+        <v>59.95934959349593</v>
       </c>
       <c r="D21" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E21" t="n">
-        <v>32.33333333333334</v>
+        <v>32.83333333333334</v>
       </c>
       <c r="F21" t="n">
-        <v>44.66666666666666</v>
+        <v>49.16666666666666</v>
       </c>
       <c r="G21" t="n">
-        <v>42.9696186109589</v>
+        <v>30.67300854776484</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1016589104767399</v>
+        <v>0.08494928482044595</v>
       </c>
       <c r="I21" t="n">
-        <v>0.06416915234022653</v>
+        <v>0.05084823917705972</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L21" t="n">
-        <v>383.7666666666667</v>
+        <v>384.2333333333333</v>
       </c>
       <c r="M21" t="n">
-        <v>28.91277788208776</v>
+        <v>15.35842404761185</v>
       </c>
       <c r="N21" t="n">
-        <v>0.09960563831298901</v>
+        <v>0.07733530289907228</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1087288900222329</v>
+        <v>0.05358727011755857</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R21" t="n">
-        <v>215.0333333333333</v>
+        <v>215.4333333333333</v>
       </c>
       <c r="S21" t="n">
-        <v>12.80849511387358</v>
+        <v>8.620325407933773</v>
       </c>
       <c r="T21" t="n">
-        <v>0.07744720319134271</v>
+        <v>0.05949749679330987</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1616391533328643</v>
+        <v>0.0649946002165398</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -3090,16 +3090,16 @@
         <v>54</v>
       </c>
       <c r="X21" t="n">
-        <v>171.1666666666667</v>
+        <v>171.2333333333333</v>
       </c>
       <c r="Y21" t="n">
-        <v>9.903544532760236</v>
+        <v>8.151389894522755</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.1002349510150407</v>
+        <v>0.08446148277893885</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.06447668680167327</v>
+        <v>0.04842403030742663</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3108,16 +3108,16 @@
         <v>43</v>
       </c>
       <c r="AD21" t="n">
-        <v>129.1333333333333</v>
+        <v>129</v>
       </c>
       <c r="AE21" t="n">
-        <v>143.6425883512746</v>
+        <v>102.7894076524927</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.1149007330783527</v>
+        <v>0.09074909031386075</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.06429703602766657</v>
+        <v>0.04857691931601338</v>
       </c>
       <c r="AH21" t="n">
         <v>0</v>
@@ -3159,28 +3159,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>41.3874469089193</v>
+        <v>41.39617607825701</v>
       </c>
       <c r="C22" t="n">
-        <v>58.61255309108069</v>
+        <v>58.60382392174299</v>
       </c>
       <c r="D22" t="n">
-        <v>70.63333333333334</v>
+        <v>74.96666666666667</v>
       </c>
       <c r="E22" t="n">
-        <v>29.23333333333333</v>
+        <v>31.03333333333333</v>
       </c>
       <c r="F22" t="n">
-        <v>41.4</v>
+        <v>43.93333333333333</v>
       </c>
       <c r="G22" t="n">
-        <v>33.12321044626474</v>
+        <v>27.13431694694344</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1130959904965577</v>
+        <v>0.09904586159312893</v>
       </c>
       <c r="I22" t="n">
-        <v>0.07180577491784719</v>
+        <v>0.05852633153125242</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -3189,16 +3189,16 @@
         <v>77</v>
       </c>
       <c r="L22" t="n">
-        <v>327.3666666666667</v>
+        <v>326.9333333333333</v>
       </c>
       <c r="M22" t="n">
-        <v>7.244309010633177</v>
+        <v>5.788080185813111</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1187951244517036</v>
+        <v>0.09657744567286854</v>
       </c>
       <c r="O22" t="n">
-        <v>0.05801782096731505</v>
+        <v>0.04400755286792676</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -3207,34 +3207,34 @@
         <v>62</v>
       </c>
       <c r="R22" t="n">
-        <v>172</v>
+        <v>172.2666666666667</v>
       </c>
       <c r="S22" t="n">
-        <v>14.73122125928603</v>
+        <v>12.2186101181559</v>
       </c>
       <c r="T22" t="n">
-        <v>0.09958555736720165</v>
+        <v>0.08578976115172995</v>
       </c>
       <c r="U22" t="n">
-        <v>0.07174224710231845</v>
+        <v>0.05859321602971614</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="W22" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X22" t="n">
-        <v>210.9</v>
+        <v>211</v>
       </c>
       <c r="Y22" t="n">
-        <v>10.57804475790173</v>
+        <v>9.013604925703241</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.09119384494933826</v>
+        <v>0.07906688670430917</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.06535794006644181</v>
+        <v>0.04771188674968246</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3243,19 +3243,19 @@
         <v>64</v>
       </c>
       <c r="AD22" t="n">
-        <v>189.5666666666667</v>
+        <v>189.7</v>
       </c>
       <c r="AE22" t="n">
-        <v>145.7464684397023</v>
+        <v>119.3431877796117</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.1281391171940239</v>
+        <v>0.1116803041463428</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.06946386723923947</v>
+        <v>0.05793258850476035</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
@@ -3294,100 +3294,100 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>29.96575342465754</v>
+        <v>29.80769230769231</v>
       </c>
       <c r="C23" t="n">
-        <v>70.03424657534246</v>
+        <v>70.19230769230771</v>
       </c>
       <c r="D23" t="n">
-        <v>58.4</v>
+        <v>58.93333333333333</v>
       </c>
       <c r="E23" t="n">
-        <v>17.5</v>
+        <v>17.56666666666667</v>
       </c>
       <c r="F23" t="n">
-        <v>40.9</v>
+        <v>41.36666666666667</v>
       </c>
       <c r="G23" t="n">
-        <v>28.9503182563154</v>
+        <v>23.14440030610455</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1451917289011913</v>
+        <v>0.1262272836752318</v>
       </c>
       <c r="I23" t="n">
-        <v>0.09512463369748735</v>
+        <v>0.08161469266502903</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L23" t="n">
-        <v>368.3333333333333</v>
+        <v>369.4</v>
       </c>
       <c r="M23" t="n">
-        <v>4.48623152980927</v>
+        <v>3.027372156604783</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1174423226370069</v>
+        <v>0.1033247763674325</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1856567980257592</v>
+        <v>0.07440451546130916</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="R23" t="n">
         <v>200.1666666666667</v>
       </c>
       <c r="S23" t="n">
-        <v>2.990828134507873</v>
+        <v>2.396608784020735</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1150115945923784</v>
+        <v>0.1182456334969979</v>
       </c>
       <c r="U23" t="n">
-        <v>0.08052500090619126</v>
+        <v>0.0812976676787209</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="X23" t="n">
-        <v>177.3666666666667</v>
+        <v>176.8333333333333</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.900795507949569</v>
+        <v>3.518983441284863</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.1236927476380621</v>
+        <v>0.1224230701273024</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.07913534934455799</v>
+        <v>0.07766765842976102</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AD23" t="n">
-        <v>153.6</v>
+        <v>153.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>201.527147069976</v>
+        <v>172.2026478176181</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.1842379209391365</v>
+        <v>0.1738745019405953</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.09737977050118196</v>
+        <v>0.07963370832170635</v>
       </c>
       <c r="AH23" t="n">
         <v>0</v>
@@ -3429,103 +3429,103 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>42.85714285714286</v>
+        <v>43.23725055432372</v>
       </c>
       <c r="C24" t="n">
-        <v>57.14285714285715</v>
+        <v>56.76274944567627</v>
       </c>
       <c r="D24" t="n">
-        <v>43.4</v>
+        <v>45.1</v>
       </c>
       <c r="E24" t="n">
-        <v>18.6</v>
+        <v>19.5</v>
       </c>
       <c r="F24" t="n">
-        <v>24.8</v>
+        <v>25.6</v>
       </c>
       <c r="G24" t="n">
-        <v>19.88491387365686</v>
+        <v>16.39856245954729</v>
       </c>
       <c r="H24" t="n">
-        <v>0.08998398997479318</v>
+        <v>0.078472392641646</v>
       </c>
       <c r="I24" t="n">
-        <v>0.05216498734325071</v>
+        <v>0.04390533586025393</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L24" t="n">
-        <v>238.4666666666667</v>
+        <v>238.6</v>
       </c>
       <c r="M24" t="n">
-        <v>7.104416738568464</v>
+        <v>5.061219443292038</v>
       </c>
       <c r="N24" t="n">
-        <v>0.07991850837547171</v>
+        <v>0.06909893741748754</v>
       </c>
       <c r="O24" t="n">
-        <v>0.05644169903892601</v>
+        <v>0.04555841232082201</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R24" t="n">
-        <v>94.8</v>
+        <v>94.63333333333334</v>
       </c>
       <c r="S24" t="n">
-        <v>30.78503333382555</v>
+        <v>22.93058614124568</v>
       </c>
       <c r="T24" t="n">
-        <v>0.08168977105163273</v>
+        <v>0.06762855497534968</v>
       </c>
       <c r="U24" t="n">
-        <v>0.08198731003871775</v>
+        <v>0.0461971734356777</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="W24" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="X24" t="n">
-        <v>341.6</v>
+        <v>341.9333333333333</v>
       </c>
       <c r="Y24" t="n">
-        <v>20.92788926455027</v>
+        <v>16.62710965818681</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.07861108643111243</v>
+        <v>0.06805252220019896</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.05553210603034364</v>
+        <v>0.04374426218127696</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AD24" t="n">
-        <v>224.8333333333333</v>
+        <v>224.7333333333333</v>
       </c>
       <c r="AE24" t="n">
-        <v>114.0664936111229</v>
+        <v>89.9420790543801</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.08757482086332993</v>
+        <v>0.07672249436460299</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.05711235641609402</v>
+        <v>0.0471159435626014</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
@@ -3564,46 +3564,46 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>26.97622996130459</v>
+        <v>26.43008474576271</v>
       </c>
       <c r="C25" t="n">
-        <v>73.0237700386954</v>
+        <v>73.56991525423729</v>
       </c>
       <c r="D25" t="n">
-        <v>60.3</v>
+        <v>62.93333333333333</v>
       </c>
       <c r="E25" t="n">
-        <v>16.26666666666667</v>
+        <v>16.63333333333333</v>
       </c>
       <c r="F25" t="n">
-        <v>44.03333333333333</v>
+        <v>46.3</v>
       </c>
       <c r="G25" t="n">
-        <v>21.47115688756961</v>
+        <v>14.31711166229107</v>
       </c>
       <c r="H25" t="n">
-        <v>0.09856280080912895</v>
+        <v>0.08140963741995508</v>
       </c>
       <c r="I25" t="n">
-        <v>0.07174828100885622</v>
+        <v>0.04981749480226581</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="L25" t="n">
-        <v>202.6333333333333</v>
+        <v>203.4333333333333</v>
       </c>
       <c r="M25" t="n">
-        <v>5.051990453734924</v>
+        <v>4.475545923872453</v>
       </c>
       <c r="N25" t="n">
-        <v>0.09934540717424921</v>
+        <v>0.08866868868643049</v>
       </c>
       <c r="O25" t="n">
-        <v>0.04615650877393575</v>
+        <v>0.03875154287285399</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -3612,34 +3612,34 @@
         <v>32</v>
       </c>
       <c r="R25" t="n">
-        <v>91.40000000000001</v>
+        <v>91.66666666666667</v>
       </c>
       <c r="S25" t="n">
-        <v>39.19895758132623</v>
+        <v>30.52836219999493</v>
       </c>
       <c r="T25" t="n">
-        <v>0.08784971220281837</v>
+        <v>0.07135715295018277</v>
       </c>
       <c r="U25" t="n">
-        <v>0.05523231338726955</v>
+        <v>0.04266247341134324</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.033333333333333</v>
       </c>
       <c r="W25" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="X25" t="n">
-        <v>406.5</v>
+        <v>405.9666666666666</v>
       </c>
       <c r="Y25" t="n">
-        <v>18.1236316941515</v>
+        <v>13.88983222939943</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.1060159920074402</v>
+        <v>0.09133994034888988</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.08080319934566201</v>
+        <v>0.06283845457856392</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3648,19 +3648,19 @@
         <v>61</v>
       </c>
       <c r="AD25" t="n">
-        <v>199.1666666666667</v>
+        <v>198.8333333333333</v>
       </c>
       <c r="AE25" t="n">
-        <v>123.1899425574048</v>
+        <v>94.78686880105988</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.1054097901050239</v>
+        <v>0.08833741879779775</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.06102022104012828</v>
+        <v>0.04952717384992378</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.033333333333333</v>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
@@ -3996,46 +3996,46 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.61658031088083</v>
+        <v>17.89473684210526</v>
       </c>
       <c r="C4" t="n">
-        <v>82.38341968911917</v>
+        <v>82.10526315789474</v>
       </c>
       <c r="D4" t="n">
-        <v>6.433333333333334</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="E4" t="n">
         <v>1.133333333333333</v>
       </c>
       <c r="F4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="G4" t="n">
-        <v>5.344069711175946</v>
+        <v>5.025009328462254</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01582544946658345</v>
+        <v>0.01440230058192481</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006156544256230654</v>
+        <v>0.006286890321353927</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="K4" t="n">
         <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>217.3333333333333</v>
+        <v>217.3</v>
       </c>
       <c r="M4" t="n">
-        <v>2.064284831112547</v>
+        <v>2.020308024669379</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04322520643162911</v>
+        <v>0.03998233580487947</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01707615844832379</v>
+        <v>0.01940493473493639</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -4044,16 +4044,16 @@
         <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>41.6</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="S4" t="n">
-        <v>1.357516141640347</v>
+        <v>1.373365753249137</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05106624402953596</v>
+        <v>0.05087590382895114</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03736398459481793</v>
+        <v>0.03847267191831125</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>3</v>
       </c>
       <c r="X4" t="n">
-        <v>20.06666666666667</v>
+        <v>20.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.702282739847471</v>
+        <v>1.597984368517491</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.04087430548560284</v>
+        <v>0.04220502493697956</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03555986890398544</v>
+        <v>0.03234881164424232</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -4080,19 +4080,19 @@
         <v>2</v>
       </c>
       <c r="AD4" t="n">
-        <v>21</v>
+        <v>20.93333333333333</v>
       </c>
       <c r="AE4" t="n">
-        <v>12.65706456548684</v>
+        <v>12.15156951387153</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.01993093250706443</v>
+        <v>0.01978014734599057</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.00793172268091713</v>
+        <v>0.008711236872133488</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
@@ -4131,46 +4131,46 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.35007610350076</v>
+        <v>10.04431314623338</v>
       </c>
       <c r="C5" t="n">
-        <v>89.64992389649925</v>
+        <v>89.95568685376662</v>
       </c>
       <c r="D5" t="n">
-        <v>21.9</v>
+        <v>22.56666666666667</v>
       </c>
       <c r="E5" t="n">
         <v>2.266666666666667</v>
       </c>
       <c r="F5" t="n">
-        <v>19.63333333333333</v>
+        <v>20.3</v>
       </c>
       <c r="G5" t="n">
-        <v>9.939927656864228</v>
+        <v>2.82884644733974</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03460230880728656</v>
+        <v>0.02710379328040334</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02614317242826836</v>
+        <v>0.01541979526496396</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="K5" t="n">
         <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>69.66666666666667</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6572559492725208</v>
+        <v>0.6746841237419549</v>
       </c>
       <c r="N5" t="n">
-        <v>0.06371895528901911</v>
+        <v>0.06018724521929186</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0257997164031829</v>
+        <v>0.0235244764013775</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -4179,55 +4179,55 @@
         <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>11.4</v>
+        <v>11.26666666666667</v>
       </c>
       <c r="S5" t="n">
-        <v>8.448721902246731</v>
+        <v>6.445007871655415</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03020591555695587</v>
+        <v>0.02268891756186278</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01716065892384565</v>
+        <v>0.01364036304534201</v>
       </c>
       <c r="V5" t="n">
-        <v>1.033333333333333</v>
+        <v>8.633333333333333</v>
       </c>
       <c r="W5" t="n">
         <v>6</v>
       </c>
       <c r="X5" t="n">
-        <v>183.9666666666667</v>
+        <v>183.6333333333333</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.851032821106603</v>
+        <v>1.620718931238349</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.04017550717232977</v>
+        <v>0.03890095142652295</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02091933972247056</v>
+        <v>0.0192166532907197</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="AC5" t="n">
         <v>3</v>
       </c>
       <c r="AD5" t="n">
-        <v>34.83333333333334</v>
+        <v>34.7</v>
       </c>
       <c r="AE5" t="n">
-        <v>23.48632953306387</v>
+        <v>13.49220102503826</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.03438897740715535</v>
+        <v>0.02950466977017155</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.01569570415127686</v>
+        <v>0.01298008855908217</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.1</v>
+        <v>15.36666666666667</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
@@ -4266,46 +4266,46 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29.81132075471698</v>
+        <v>28.24427480916031</v>
       </c>
       <c r="C6" t="n">
-        <v>70.18867924528303</v>
+        <v>71.7557251908397</v>
       </c>
       <c r="D6" t="n">
-        <v>26.5</v>
+        <v>26.2</v>
       </c>
       <c r="E6" t="n">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="F6" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="G6" t="n">
-        <v>11.19456334987902</v>
+        <v>8.117714516267549</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03926093605106565</v>
+        <v>0.03433564998752204</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0230355470205596</v>
+        <v>0.0197880187963423</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L6" t="n">
-        <v>202.9</v>
+        <v>203.6333333333333</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4162964748906475</v>
+        <v>0.3987611352901644</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0732914303286305</v>
+        <v>0.06846614121406525</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0199249698730215</v>
+        <v>0.01966102821086513</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -4314,16 +4314,16 @@
         <v>8</v>
       </c>
       <c r="R6" t="n">
-        <v>19.03333333333333</v>
+        <v>18.86666666666667</v>
       </c>
       <c r="S6" t="n">
-        <v>1.598366821146497</v>
+        <v>1.525703001814728</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0583830401922546</v>
+        <v>0.05798506061258306</v>
       </c>
       <c r="U6" t="n">
-        <v>0.04026468873368676</v>
+        <v>0.03543481744123921</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -4332,16 +4332,16 @@
         <v>6</v>
       </c>
       <c r="X6" t="n">
-        <v>26.36666666666667</v>
+        <v>26.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.863729017706243</v>
+        <v>2.611390841733373</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.04800537470455413</v>
+        <v>0.04356044841507091</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0265065089395372</v>
+        <v>0.02357410496263139</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -4350,16 +4350,16 @@
         <v>5</v>
       </c>
       <c r="AD6" t="n">
-        <v>51.06666666666667</v>
+        <v>51.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>19.78208800686201</v>
+        <v>16.05028244971529</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.03886989642428806</v>
+        <v>0.03458820244705241</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.01842565814399949</v>
+        <v>0.01563618493099039</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
@@ -4399,31 +4399,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21.05263157894737</v>
+        <v>21.875</v>
       </c>
       <c r="C7" t="n">
-        <v>78.94736842105264</v>
+        <v>78.12500000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>8.233333333333333</v>
+        <v>8.533333333333333</v>
       </c>
       <c r="E7" t="n">
-        <v>1.733333333333333</v>
+        <v>1.866666666666667</v>
       </c>
       <c r="F7" t="n">
-        <v>6.5</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G7" t="n">
-        <v>6.656592110820375</v>
+        <v>5.521958158556984</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02591313987202839</v>
+        <v>0.02185774213597417</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00956323437552435</v>
+        <v>0.006649312501850226</v>
       </c>
       <c r="J7" t="n">
-        <v>1.033333333333333</v>
+        <v>11.56666666666667</v>
       </c>
       <c r="K7" t="n">
         <v>4</v>
@@ -4432,13 +4432,13 @@
         <v>214.6666666666667</v>
       </c>
       <c r="M7" t="n">
-        <v>2.463497395589005</v>
+        <v>1.05425493694261</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0438850478612336</v>
+        <v>0.03422011486738658</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02219589427909823</v>
+        <v>0.01482790637048901</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -4447,16 +4447,16 @@
         <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>21.1</v>
+        <v>21.13333333333333</v>
       </c>
       <c r="S7" t="n">
-        <v>5.371730815014979</v>
+        <v>2.33450016143448</v>
       </c>
       <c r="T7" t="n">
-        <v>0.08191952957861603</v>
+        <v>0.06517777027195758</v>
       </c>
       <c r="U7" t="n">
-        <v>0.06410702855488636</v>
+        <v>0.04470671364528153</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -4465,16 +4465,16 @@
         <v>3</v>
       </c>
       <c r="X7" t="n">
-        <v>27.26666666666667</v>
+        <v>27.33333333333333</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.448802032648931</v>
+        <v>2.044084649087194</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.05186675616717445</v>
+        <v>0.043131805488352</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.02325099286933202</v>
+        <v>0.02329609175435461</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -4486,16 +4486,16 @@
         <v>36.86666666666667</v>
       </c>
       <c r="AE7" t="n">
-        <v>17.6115099068632</v>
+        <v>11.55078368754145</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.03543125399627958</v>
+        <v>0.0272321738050201</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0112890068975609</v>
+        <v>0.009708401622578744</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.033333333333333</v>
+        <v>11.56666666666667</v>
       </c>
       <c r="AI7" t="n">
         <v>385</v>
@@ -4532,28 +4532,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>15.51724137931035</v>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>84.48275862068967</v>
       </c>
       <c r="D8" t="n">
-        <v>5.9</v>
+        <v>7.733333333333333</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="F8" t="n">
-        <v>5.9</v>
+        <v>6.533333333333333</v>
       </c>
       <c r="G8" t="n">
-        <v>3.205923085631998</v>
+        <v>3.177202593610174</v>
       </c>
       <c r="H8" t="n">
-        <v>0.05020685226190388</v>
+        <v>0.04807692819671013</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03689606855951931</v>
+        <v>0.0354568468247428</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -4562,16 +4562,16 @@
         <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>46.56666666666667</v>
+        <v>46.46666666666667</v>
       </c>
       <c r="M8" t="n">
-        <v>3.476252575851405</v>
+        <v>3.21041292033766</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03201574602493999</v>
+        <v>0.02785546512740438</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01823590630871774</v>
+        <v>0.01843457101100127</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -4580,34 +4580,34 @@
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>79.06666666666666</v>
+        <v>79.46666666666667</v>
       </c>
       <c r="S8" t="n">
-        <v>4.111840235291716</v>
+        <v>3.895648699395969</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03503549095226183</v>
+        <v>0.03288763914949119</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02029844014975043</v>
+        <v>0.01946128512742889</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.033333333333333</v>
       </c>
       <c r="W8" t="n">
         <v>9</v>
       </c>
       <c r="X8" t="n">
-        <v>82.59999999999999</v>
+        <v>82.53333333333333</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.535422963075958</v>
+        <v>3.482009941222969</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.02870877872072489</v>
+        <v>0.0262674140035918</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01771123456634528</v>
+        <v>0.01717457433700693</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -4616,19 +4616,19 @@
         <v>12</v>
       </c>
       <c r="AD8" t="n">
-        <v>91.59999999999999</v>
+        <v>91.53333333333333</v>
       </c>
       <c r="AE8" t="n">
-        <v>18.28401119912527</v>
+        <v>16.82978968047633</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.03468464024161524</v>
+        <v>0.03265109352620599</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.01976304035277088</v>
+        <v>0.01759258800265118</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.033333333333333</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
@@ -4667,28 +4667,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41.11675126903553</v>
+        <v>37.88546255506608</v>
       </c>
       <c r="C9" t="n">
-        <v>58.88324873096447</v>
+        <v>62.11453744493392</v>
       </c>
       <c r="D9" t="n">
-        <v>13.13333333333333</v>
+        <v>15.13333333333333</v>
       </c>
       <c r="E9" t="n">
-        <v>5.4</v>
+        <v>5.733333333333333</v>
       </c>
       <c r="F9" t="n">
-        <v>7.733333333333333</v>
+        <v>9.4</v>
       </c>
       <c r="G9" t="n">
-        <v>5.52768099696012</v>
+        <v>5.109049382531162</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06226877755040696</v>
+        <v>0.06176226674760639</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03278170898988762</v>
+        <v>0.03486467662218418</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -4697,16 +4697,16 @@
         <v>16</v>
       </c>
       <c r="L9" t="n">
-        <v>78.2</v>
+        <v>78.16666666666667</v>
       </c>
       <c r="M9" t="n">
-        <v>4.412496338951229</v>
+        <v>4.026666263113416</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05551279525153478</v>
+        <v>0.05194321667445972</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03492561227295479</v>
+        <v>0.03337166119457315</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -4715,16 +4715,16 @@
         <v>16</v>
       </c>
       <c r="R9" t="n">
-        <v>84.8</v>
+        <v>84.73333333333333</v>
       </c>
       <c r="S9" t="n">
-        <v>6.726015604361963</v>
+        <v>6.237862225067254</v>
       </c>
       <c r="T9" t="n">
-        <v>0.06759129187754986</v>
+        <v>0.06668638687814044</v>
       </c>
       <c r="U9" t="n">
-        <v>0.04625584465185142</v>
+        <v>0.04323004318736588</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -4733,16 +4733,16 @@
         <v>10</v>
       </c>
       <c r="X9" t="n">
-        <v>77.09999999999999</v>
+        <v>77.23333333333333</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.656673200621924</v>
+        <v>3.535675928087899</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.05025422847466907</v>
+        <v>0.04799964477010289</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.02559138697102565</v>
+        <v>0.02377367954997886</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -4751,16 +4751,16 @@
         <v>9</v>
       </c>
       <c r="AD9" t="n">
-        <v>59.9</v>
+        <v>59.86666666666667</v>
       </c>
       <c r="AE9" t="n">
-        <v>23.84302873070984</v>
+        <v>22.27667043747478</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.05611923666044238</v>
+        <v>0.05302582984238813</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.02573167536786514</v>
+        <v>0.02664103654234606</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
@@ -4802,28 +4802,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>40.5759162303665</v>
+        <v>43.04812834224599</v>
       </c>
       <c r="C10" t="n">
-        <v>59.42408376963351</v>
+        <v>56.95187165775401</v>
       </c>
       <c r="D10" t="n">
-        <v>12.73333333333333</v>
+        <v>12.46666666666667</v>
       </c>
       <c r="E10" t="n">
-        <v>5.166666666666667</v>
+        <v>5.366666666666666</v>
       </c>
       <c r="F10" t="n">
-        <v>7.566666666666666</v>
+        <v>7.1</v>
       </c>
       <c r="G10" t="n">
-        <v>6.425159063916263</v>
+        <v>6.059029331548308</v>
       </c>
       <c r="H10" t="n">
-        <v>0.05021575629860999</v>
+        <v>0.04787522299282979</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02795499059313055</v>
+        <v>0.02625239445118562</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -4832,16 +4832,16 @@
         <v>10</v>
       </c>
       <c r="L10" t="n">
-        <v>89.36666666666666</v>
+        <v>89.3</v>
       </c>
       <c r="M10" t="n">
-        <v>5.287319021735607</v>
+        <v>5.368941818218582</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05833165839659123</v>
+        <v>0.06151276230712393</v>
       </c>
       <c r="O10" t="n">
-        <v>0.03710219052700835</v>
+        <v>0.03859707780117168</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -4850,16 +4850,16 @@
         <v>12</v>
       </c>
       <c r="R10" t="n">
-        <v>83.16666666666667</v>
+        <v>83.23333333333333</v>
       </c>
       <c r="S10" t="n">
-        <v>4.976119043035989</v>
+        <v>4.998968357776591</v>
       </c>
       <c r="T10" t="n">
-        <v>0.05652716317847625</v>
+        <v>0.05758231959527586</v>
       </c>
       <c r="U10" t="n">
-        <v>0.05379344769516944</v>
+        <v>0.05027669430962816</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -4868,16 +4868,16 @@
         <v>16</v>
       </c>
       <c r="X10" t="n">
-        <v>66.03333333333333</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.641270685903129</v>
+        <v>2.650141401313071</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.05324819872078171</v>
+        <v>0.05375810432252904</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.02082030587696164</v>
+        <v>0.02095967248314594</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -4886,16 +4886,16 @@
         <v>18</v>
       </c>
       <c r="AD10" t="n">
-        <v>61.4</v>
+        <v>61.06666666666667</v>
       </c>
       <c r="AE10" t="n">
-        <v>23.67615769958066</v>
+        <v>23.40308617915528</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.06251953486355266</v>
+        <v>0.06498998151314886</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.02911064510450379</v>
+        <v>0.02698538098830416</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
@@ -4937,28 +4937,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>46.92737430167598</v>
+        <v>48.90109890109891</v>
       </c>
       <c r="C11" t="n">
-        <v>53.07262569832402</v>
+        <v>51.0989010989011</v>
       </c>
       <c r="D11" t="n">
-        <v>5.966666666666667</v>
+        <v>6.066666666666666</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8</v>
+        <v>2.966666666666667</v>
       </c>
       <c r="F11" t="n">
-        <v>3.166666666666667</v>
+        <v>3.1</v>
       </c>
       <c r="G11" t="n">
-        <v>6.073960802490126</v>
+        <v>4.919531055234684</v>
       </c>
       <c r="H11" t="n">
-        <v>0.02953314309690427</v>
+        <v>0.02796226418243999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01402703784167659</v>
+        <v>0.01283450335957736</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -4967,16 +4967,16 @@
         <v>9</v>
       </c>
       <c r="L11" t="n">
-        <v>192.0333333333333</v>
+        <v>192.0666666666667</v>
       </c>
       <c r="M11" t="n">
-        <v>2.544074509293904</v>
+        <v>2.280872153751346</v>
       </c>
       <c r="N11" t="n">
-        <v>0.03462733984855517</v>
+        <v>0.03152976741138158</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01839832298885578</v>
+        <v>0.01404148979782763</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -4985,16 +4985,16 @@
         <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>68.59999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="S11" t="n">
-        <v>1.687833851588869</v>
+        <v>1.642654874399019</v>
       </c>
       <c r="T11" t="n">
-        <v>0.05755637044217782</v>
+        <v>0.05783347591230729</v>
       </c>
       <c r="U11" t="n">
-        <v>0.02674585413066986</v>
+        <v>0.02697654284298232</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -5003,16 +5003,16 @@
         <v>6</v>
       </c>
       <c r="X11" t="n">
-        <v>30.13333333333333</v>
+        <v>30.06666666666667</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4337979403577376</v>
+        <v>0.4298672043355134</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.07022632211368485</v>
+        <v>0.0701593898637789</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.03429497712207163</v>
+        <v>0.03345968460362303</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -5021,16 +5021,16 @@
         <v>4</v>
       </c>
       <c r="AD11" t="n">
-        <v>9.233333333333333</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="AE11" t="n">
-        <v>16.20036548409057</v>
+        <v>13.96081172101484</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.03125628886084589</v>
+        <v>0.0282517721892328</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.01593160759247081</v>
+        <v>0.01437141878787707</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
@@ -5072,28 +5072,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>51.47058823529412</v>
+        <v>45.23809523809523</v>
       </c>
       <c r="C12" t="n">
-        <v>48.52941176470589</v>
+        <v>54.76190476190475</v>
       </c>
       <c r="D12" t="n">
-        <v>4.533333333333333</v>
+        <v>4.2</v>
       </c>
       <c r="E12" t="n">
-        <v>2.333333333333333</v>
+        <v>1.9</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="G12" t="n">
-        <v>2.084955944837741</v>
+        <v>1.205817466044951</v>
       </c>
       <c r="H12" t="n">
-        <v>0.05147800160981936</v>
+        <v>0.03406434818096662</v>
       </c>
       <c r="I12" t="n">
-        <v>0.03759699718198559</v>
+        <v>0.04275568812764</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -5102,34 +5102,34 @@
         <v>6</v>
       </c>
       <c r="L12" t="n">
-        <v>31.43333333333333</v>
+        <v>31.63333333333333</v>
       </c>
       <c r="M12" t="n">
-        <v>3.453238981484236</v>
+        <v>2.28300169323857</v>
       </c>
       <c r="N12" t="n">
-        <v>0.02319477735491796</v>
+        <v>0.01575716019860425</v>
       </c>
       <c r="O12" t="n">
-        <v>0.01244098373186238</v>
+        <v>0.009526001908705218</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>7.733333333333333</v>
       </c>
       <c r="Q12" t="n">
         <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>53.66666666666666</v>
+        <v>53.63333333333333</v>
       </c>
       <c r="S12" t="n">
-        <v>9.408607366412056</v>
+        <v>4.832385630700447</v>
       </c>
       <c r="T12" t="n">
-        <v>0.04742132884698722</v>
+        <v>0.02214259822031626</v>
       </c>
       <c r="U12" t="n">
-        <v>0.01586495577873085</v>
+        <v>0.007277581428170971</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -5138,16 +5138,16 @@
         <v>7</v>
       </c>
       <c r="X12" t="n">
-        <v>171.9666666666667</v>
+        <v>171.7666666666667</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.356248807678214</v>
+        <v>2.48630204747254</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.06457437883234476</v>
+        <v>0.05152623651533965</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.03348341152540454</v>
+        <v>0.02702580298493741</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -5156,19 +5156,19 @@
         <v>5</v>
       </c>
       <c r="AD12" t="n">
-        <v>42.83333333333334</v>
+        <v>42.96666666666667</v>
       </c>
       <c r="AE12" t="n">
-        <v>23.95457987095037</v>
+        <v>14.49499051580439</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.05167528236273858</v>
+        <v>0.02569376447030197</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.01965892817501474</v>
+        <v>0.01035018812126387</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AI12" t="n">
         <v>385</v>
@@ -5205,28 +5205,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>61.6</v>
+        <v>57.74647887323943</v>
       </c>
       <c r="C13" t="n">
-        <v>38.4</v>
+        <v>42.25352112676056</v>
       </c>
       <c r="D13" t="n">
-        <v>4.166666666666667</v>
+        <v>4.733333333333333</v>
       </c>
       <c r="E13" t="n">
-        <v>2.566666666666667</v>
+        <v>2.733333333333333</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>5.8535970232964</v>
+        <v>3.279556675605357</v>
       </c>
       <c r="H13" t="n">
-        <v>0.08652850697586209</v>
+        <v>0.06195084103167665</v>
       </c>
       <c r="I13" t="n">
-        <v>0.05238986604838294</v>
+        <v>0.03426989380691643</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -5235,16 +5235,16 @@
         <v>3</v>
       </c>
       <c r="L13" t="n">
-        <v>42.63333333333333</v>
+        <v>42.33333333333334</v>
       </c>
       <c r="M13" t="n">
-        <v>12.45391651274156</v>
+        <v>4.853123978711912</v>
       </c>
       <c r="N13" t="n">
-        <v>0.06924782223529566</v>
+        <v>0.04330431041888459</v>
       </c>
       <c r="O13" t="n">
-        <v>0.06114305171402493</v>
+        <v>0.03067467479069124</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -5253,16 +5253,16 @@
         <v>8</v>
       </c>
       <c r="R13" t="n">
-        <v>95.5</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>4.281913313967074</v>
+        <v>1.237366634286901</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0766328053265137</v>
+        <v>0.054077083998656</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0358647688714149</v>
+        <v>0.02988001408283969</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -5274,34 +5274,34 @@
         <v>20.23333333333333</v>
       </c>
       <c r="Y13" t="n">
-        <v>12.11440892596454</v>
+        <v>7.116226300096804</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.04572857517786795</v>
+        <v>0.0392719650367515</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.0359223682559282</v>
+        <v>0.01893287732482565</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="AC13" t="n">
         <v>6</v>
       </c>
       <c r="AD13" t="n">
-        <v>141.1666666666667</v>
+        <v>141.3333333333333</v>
       </c>
       <c r="AE13" t="n">
-        <v>41.90604838951498</v>
+        <v>18.75733040690471</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.05743330312345618</v>
+        <v>0.042519096112623</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.03021703931873343</v>
+        <v>0.02183153227146495</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="AI13" t="n">
         <v>385</v>
@@ -5338,28 +5338,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>61.39240506329114</v>
+        <v>61.05919003115265</v>
       </c>
       <c r="C14" t="n">
-        <v>38.60759493670886</v>
+        <v>38.94080996884735</v>
       </c>
       <c r="D14" t="n">
-        <v>10.53333333333333</v>
+        <v>10.7</v>
       </c>
       <c r="E14" t="n">
-        <v>6.466666666666667</v>
+        <v>6.533333333333333</v>
       </c>
       <c r="F14" t="n">
-        <v>4.066666666666666</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="G14" t="n">
-        <v>6.018710014145602</v>
+        <v>3.309289102561001</v>
       </c>
       <c r="H14" t="n">
-        <v>0.07376304127707661</v>
+        <v>0.06046611235689291</v>
       </c>
       <c r="I14" t="n">
-        <v>0.109661198528949</v>
+        <v>0.02670677016748517</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -5368,16 +5368,16 @@
         <v>5</v>
       </c>
       <c r="L14" t="n">
-        <v>51.76666666666667</v>
+        <v>51.96666666666667</v>
       </c>
       <c r="M14" t="n">
-        <v>2.545894731835969</v>
+        <v>2.149917400231496</v>
       </c>
       <c r="N14" t="n">
-        <v>0.06021446953188749</v>
+        <v>0.05235583792633441</v>
       </c>
       <c r="O14" t="n">
-        <v>0.03466888965585386</v>
+        <v>0.02333740483885388</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -5386,55 +5386,55 @@
         <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>30.83333333333333</v>
+        <v>30.9</v>
       </c>
       <c r="S14" t="n">
-        <v>14.28303005130982</v>
+        <v>5.187622926406128</v>
       </c>
       <c r="T14" t="n">
-        <v>0.04110190174865008</v>
+        <v>0.02675389245891708</v>
       </c>
       <c r="U14" t="n">
-        <v>0.02754892044541392</v>
+        <v>0.01601051299356904</v>
       </c>
       <c r="V14" t="n">
-        <v>1.066666666666667</v>
+        <v>12.2</v>
       </c>
       <c r="W14" t="n">
         <v>8</v>
       </c>
       <c r="X14" t="n">
-        <v>110.9</v>
+        <v>111.1333333333333</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.059999185401014</v>
+        <v>3.78183000528414</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.03674610542471404</v>
+        <v>0.02670714617715003</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.02192590856925896</v>
+        <v>0.01872225156747418</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.033333333333333</v>
       </c>
       <c r="AC14" t="n">
         <v>6</v>
       </c>
       <c r="AD14" t="n">
-        <v>106.1666666666667</v>
+        <v>106</v>
       </c>
       <c r="AE14" t="n">
-        <v>31.22698152368491</v>
+        <v>16.12044916782985</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.04722358560849582</v>
+        <v>0.03544272257657372</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.02716869338830108</v>
+        <v>0.01879801299796985</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.066666666666667</v>
+        <v>13.23333333333333</v>
       </c>
       <c r="AI14" t="n">
         <v>385</v>
@@ -5471,46 +5471,46 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>51.75257731958763</v>
+        <v>50.38022813688212</v>
       </c>
       <c r="C15" t="n">
-        <v>48.24742268041237</v>
+        <v>49.61977186311786</v>
       </c>
       <c r="D15" t="n">
-        <v>16.16666666666667</v>
+        <v>17.53333333333333</v>
       </c>
       <c r="E15" t="n">
-        <v>8.366666666666667</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="F15" t="n">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>2.225491241589283</v>
+        <v>1.521596119285132</v>
       </c>
       <c r="H15" t="n">
-        <v>0.06032584722687705</v>
+        <v>0.04067672295756041</v>
       </c>
       <c r="I15" t="n">
-        <v>0.02917569844904344</v>
+        <v>0.02717795734519259</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L15" t="n">
-        <v>31.9</v>
+        <v>31.6</v>
       </c>
       <c r="M15" t="n">
-        <v>4.771932481097862</v>
+        <v>2.318620033970879</v>
       </c>
       <c r="N15" t="n">
-        <v>0.06432365671071399</v>
+        <v>0.04037221788262425</v>
       </c>
       <c r="O15" t="n">
-        <v>0.03761986135747148</v>
+        <v>0.02756789303773237</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -5519,55 +5519,55 @@
         <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>44.03333333333333</v>
+        <v>43.93333333333333</v>
       </c>
       <c r="S15" t="n">
-        <v>21.5881096503685</v>
+        <v>6.70946317568741</v>
       </c>
       <c r="T15" t="n">
-        <v>0.04647115463107953</v>
+        <v>0.01894747298041704</v>
       </c>
       <c r="U15" t="n">
-        <v>0.08879713004245822</v>
+        <v>0.01639843596619687</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>14.26666666666667</v>
       </c>
       <c r="W15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X15" t="n">
-        <v>123.0333333333333</v>
+        <v>123.3</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.349836627351158</v>
+        <v>1.813378066847518</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.02111115886642397</v>
+        <v>0.01372293643865298</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.01990728788950007</v>
+        <v>0.007328200041961464</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.033333333333333</v>
+        <v>43.46666666666667</v>
       </c>
       <c r="AC15" t="n">
         <v>3</v>
       </c>
       <c r="AD15" t="n">
-        <v>100.8666666666667</v>
+        <v>101.1666666666667</v>
       </c>
       <c r="AE15" t="n">
-        <v>34.40148952861156</v>
+        <v>13.0773672416689</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.0389601534826256</v>
+        <v>0.01831320069869297</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.01885265605523578</v>
+        <v>0.01106743970635371</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.033333333333333</v>
+        <v>58.86666666666667</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
@@ -5606,46 +5606,46 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6.846473029045644</v>
+        <v>12.12653778558875</v>
       </c>
       <c r="C16" t="n">
-        <v>93.15352697095436</v>
+        <v>87.87346221441126</v>
       </c>
       <c r="D16" t="n">
-        <v>16.06666666666667</v>
+        <v>18.96666666666667</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="F16" t="n">
-        <v>14.96666666666667</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="G16" t="n">
-        <v>2.506575790195172</v>
+        <v>1.852437762202108</v>
       </c>
       <c r="H16" t="n">
-        <v>0.07047018425363666</v>
+        <v>0.06239899206304504</v>
       </c>
       <c r="I16" t="n">
-        <v>0.06524312340547475</v>
+        <v>0.0566340422832959</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L16" t="n">
-        <v>25.93333333333333</v>
+        <v>24.46666666666667</v>
       </c>
       <c r="M16" t="n">
-        <v>13.90361718111832</v>
+        <v>3.88298678016181</v>
       </c>
       <c r="N16" t="n">
-        <v>0.06735656535166984</v>
+        <v>0.04636486932528758</v>
       </c>
       <c r="O16" t="n">
-        <v>0.07390520458349177</v>
+        <v>0.02673625026435034</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -5654,55 +5654,55 @@
         <v>6</v>
       </c>
       <c r="R16" t="n">
-        <v>60.93333333333333</v>
+        <v>61.5</v>
       </c>
       <c r="S16" t="n">
-        <v>8.986144550100308</v>
+        <v>4.665224998118616</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0583332688763051</v>
+        <v>0.04182510873102085</v>
       </c>
       <c r="U16" t="n">
-        <v>0.04045142447781746</v>
+        <v>0.02313282334059341</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X16" t="n">
         <v>84.09999999999999</v>
       </c>
       <c r="Y16" t="n">
-        <v>25.53455261143245</v>
+        <v>4.698135459637054</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.04095878658244613</v>
+        <v>0.02824767544593999</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.02498005947951985</v>
+        <v>0.01059163019225063</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="AC16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AD16" t="n">
-        <v>128.1333333333333</v>
+        <v>129.9333333333333</v>
       </c>
       <c r="AE16" t="n">
-        <v>58.12564566231841</v>
+        <v>16.13870784947341</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.0574887762232717</v>
+        <v>0.03897357937253032</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.02834139570447902</v>
+        <v>0.01761408718301272</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
@@ -5741,28 +5741,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>27.47524752475248</v>
+        <v>30.57644110275689</v>
       </c>
       <c r="C17" t="n">
-        <v>72.52475247524752</v>
+        <v>69.4235588972431</v>
       </c>
       <c r="D17" t="n">
-        <v>13.46666666666667</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="n">
-        <v>3.7</v>
+        <v>4.066666666666666</v>
       </c>
       <c r="F17" t="n">
-        <v>9.766666666666667</v>
+        <v>9.233333333333333</v>
       </c>
       <c r="G17" t="n">
-        <v>2.708443067229616</v>
+        <v>2.307771058457939</v>
       </c>
       <c r="H17" t="n">
-        <v>0.06657922810900112</v>
+        <v>0.06248750218272168</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0303805657057715</v>
+        <v>0.03321108294821435</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -5771,16 +5771,16 @@
         <v>11</v>
       </c>
       <c r="L17" t="n">
-        <v>40.83333333333334</v>
+        <v>39.93333333333333</v>
       </c>
       <c r="M17" t="n">
-        <v>10.20279575733561</v>
+        <v>5.328038251962928</v>
       </c>
       <c r="N17" t="n">
-        <v>0.05535057876616815</v>
+        <v>0.05574561811257165</v>
       </c>
       <c r="O17" t="n">
-        <v>0.04779347997833457</v>
+        <v>0.04520961173164794</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -5789,55 +5789,55 @@
         <v>8</v>
       </c>
       <c r="R17" t="n">
-        <v>66.56666666666666</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="S17" t="n">
-        <v>4.393919858389814</v>
+        <v>3.998214266312129</v>
       </c>
       <c r="T17" t="n">
-        <v>0.05949137735103857</v>
+        <v>0.05430206677012897</v>
       </c>
       <c r="U17" t="n">
-        <v>0.02291567740208962</v>
+        <v>0.02007194629197874</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
+        <v>6</v>
+      </c>
+      <c r="X17" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>6.036888720530756</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.03033000674497989</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.02403619697267943</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC17" t="n">
         <v>5</v>
       </c>
-      <c r="X17" t="n">
-        <v>69</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>24.90777401901407</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0.03745444001927674</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0.07940157575702156</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>8</v>
-      </c>
       <c r="AD17" t="n">
-        <v>120.7333333333333</v>
+        <v>124.1</v>
       </c>
       <c r="AE17" t="n">
-        <v>52.81839902791936</v>
+        <v>19.58332643802149</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.05513450557737831</v>
+        <v>0.04897744374015095</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.03140158024523487</v>
+        <v>0.02571571836197695</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.133333333333333</v>
+        <v>1.2</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
@@ -5876,103 +5876,103 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24.61538461538461</v>
+        <v>27.53623188405797</v>
       </c>
       <c r="C18" t="n">
-        <v>75.38461538461537</v>
+        <v>72.46376811594203</v>
       </c>
       <c r="D18" t="n">
-        <v>10.83333333333333</v>
+        <v>11.5</v>
       </c>
       <c r="E18" t="n">
-        <v>2.666666666666667</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="F18" t="n">
-        <v>8.166666666666666</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G18" t="n">
-        <v>1.575749037126535</v>
+        <v>1.114647740558452</v>
       </c>
       <c r="H18" t="n">
-        <v>0.04972774173117735</v>
+        <v>0.03747114375769945</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0118823947339017</v>
+        <v>0.01552376036050997</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>2.066666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L18" t="n">
-        <v>28.73333333333333</v>
+        <v>27.2</v>
       </c>
       <c r="M18" t="n">
-        <v>17.33002171914923</v>
+        <v>3.794838128186221</v>
       </c>
       <c r="N18" t="n">
-        <v>0.06537636158784772</v>
+        <v>0.03909550171188499</v>
       </c>
       <c r="O18" t="n">
-        <v>0.08251799367409007</v>
+        <v>0.03066424909270781</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="Q18" t="n">
         <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>43.26666666666667</v>
+        <v>43.56666666666667</v>
       </c>
       <c r="S18" t="n">
-        <v>8.633369739414732</v>
+        <v>1.669584554636883</v>
       </c>
       <c r="T18" t="n">
-        <v>0.09566568387390563</v>
+        <v>0.04823044374347923</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1622743426658098</v>
+        <v>0.03089818854864791</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
+        <v>3</v>
+      </c>
+      <c r="X18" t="n">
+        <v>33.13333333333333</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>3.804099618702796</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.01552660115118127</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.006809132442191157</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>21.73333333333333</v>
+      </c>
+      <c r="AC18" t="n">
         <v>4</v>
       </c>
-      <c r="X18" t="n">
-        <v>32.23333333333333</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>30.04009320310416</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0.03314016291373879</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0.02300015429447292</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>5</v>
-      </c>
       <c r="AD18" t="n">
-        <v>194.4333333333333</v>
+        <v>196.1</v>
       </c>
       <c r="AE18" t="n">
-        <v>63.62067443425587</v>
+        <v>11.03488576188224</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.04418026713049245</v>
+        <v>0.02051224906101567</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.02618667199593572</v>
+        <v>0.0105076889228054</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>29.7</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
@@ -6011,28 +6011,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>50</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="C19" t="n">
-        <v>50</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="D19" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="F19" t="n">
-        <v>2.3</v>
+        <v>1.866666666666667</v>
       </c>
       <c r="G19" t="n">
-        <v>1.489018947431196</v>
+        <v>1.124984984346085</v>
       </c>
       <c r="H19" t="n">
-        <v>0.06196518040612622</v>
+        <v>0.04905344695644494</v>
       </c>
       <c r="I19" t="n">
-        <v>0.06338081776150628</v>
+        <v>0.01858409258039071</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -6041,73 +6041,73 @@
         <v>3</v>
       </c>
       <c r="L19" t="n">
-        <v>20.63333333333333</v>
+        <v>20.7</v>
       </c>
       <c r="M19" t="n">
-        <v>7.372871796499552</v>
+        <v>3.871042803161242</v>
       </c>
       <c r="N19" t="n">
-        <v>0.03181741947039407</v>
+        <v>0.02418232862122945</v>
       </c>
       <c r="O19" t="n">
-        <v>0.01880993661129551</v>
+        <v>0.01055455214849293</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q19" t="n">
         <v>6</v>
       </c>
       <c r="R19" t="n">
-        <v>119.4</v>
+        <v>119.5666666666667</v>
       </c>
       <c r="S19" t="n">
-        <v>11.17276476802436</v>
+        <v>5.416409554490587</v>
       </c>
       <c r="T19" t="n">
-        <v>0.05238064666812317</v>
+        <v>0.03470481753601792</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1308300317025474</v>
+        <v>0.03401353392507001</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X19" t="n">
-        <v>81.63333333333334</v>
+        <v>81.7</v>
       </c>
       <c r="Y19" t="n">
-        <v>3.876080670931625</v>
+        <v>2.696906371761528</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.03764673984929356</v>
+        <v>0.02617498025971299</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.01966837141119265</v>
+        <v>0.01455239469335955</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD19" t="n">
-        <v>78.26666666666667</v>
+        <v>78.03333333333333</v>
       </c>
       <c r="AE19" t="n">
-        <v>25.69854138745389</v>
+        <v>14.55214023366701</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.03449323672572369</v>
+        <v>0.01939400205514685</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.01716979678972042</v>
+        <v>0.01078681015548966</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
@@ -6146,49 +6146,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>58.33333333333334</v>
+        <v>60</v>
       </c>
       <c r="C20" t="n">
-        <v>41.66666666666667</v>
+        <v>39.99999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>2.8</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="E20" t="n">
-        <v>1.633333333333333</v>
+        <v>1.7</v>
       </c>
       <c r="F20" t="n">
-        <v>1.166666666666667</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="G20" t="n">
-        <v>4.29514050031186</v>
+        <v>1.890809581361524</v>
       </c>
       <c r="H20" t="n">
-        <v>0.03880725024137669</v>
+        <v>0.01465203754201464</v>
       </c>
       <c r="I20" t="n">
-        <v>0.01764231094332122</v>
+        <v>0.007827622828969802</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="K20" t="n">
         <v>5</v>
       </c>
       <c r="L20" t="n">
-        <v>130.3666666666667</v>
+        <v>130</v>
       </c>
       <c r="M20" t="n">
-        <v>2.807322574148285</v>
+        <v>1.084767711448644</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0660572583408401</v>
+        <v>0.05338563822756817</v>
       </c>
       <c r="O20" t="n">
-        <v>0.04491911583550651</v>
+        <v>0.03099904869325</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Q20" t="n">
         <v>3</v>
@@ -6197,52 +6197,52 @@
         <v>16.93333333333333</v>
       </c>
       <c r="S20" t="n">
-        <v>29.34173672619398</v>
+        <v>6.689659032147547</v>
       </c>
       <c r="T20" t="n">
-        <v>0.04157517023878923</v>
+        <v>0.01097523921821345</v>
       </c>
       <c r="U20" t="n">
-        <v>0.020554248299968</v>
+        <v>0.005646068074833372</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>20.8</v>
       </c>
       <c r="W20" t="n">
         <v>2</v>
       </c>
       <c r="X20" t="n">
-        <v>125.9666666666667</v>
+        <v>126.5666666666667</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.352007507895914</v>
+        <v>0.6082397934502342</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.04643389730735881</v>
+        <v>0.01448802964317375</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.01111247315705288</v>
+        <v>0.009139634649197592</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC20" t="n">
         <v>1</v>
       </c>
       <c r="AD20" t="n">
-        <v>26.56666666666667</v>
+        <v>26.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>39.92332109270018</v>
+        <v>11.33063476965921</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.04092321899746648</v>
+        <v>0.01260484668484879</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.01707658627340991</v>
+        <v>0.005781203430892723</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>38.83333333333334</v>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
@@ -6281,46 +6281,46 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>33.44051446945338</v>
+        <v>27.2189349112426</v>
       </c>
       <c r="C21" t="n">
-        <v>66.55948553054662</v>
+        <v>72.78106508875739</v>
       </c>
       <c r="D21" t="n">
-        <v>10.36666666666667</v>
+        <v>11.26666666666667</v>
       </c>
       <c r="E21" t="n">
-        <v>3.466666666666667</v>
+        <v>3.066666666666667</v>
       </c>
       <c r="F21" t="n">
-        <v>6.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>9.638536532353033</v>
+        <v>6.441548664463999</v>
       </c>
       <c r="H21" t="n">
-        <v>0.05813571635891573</v>
+        <v>0.04463724430916336</v>
       </c>
       <c r="I21" t="n">
-        <v>0.03593002625554023</v>
+        <v>0.02806884717973584</v>
       </c>
       <c r="J21" t="n">
-        <v>1.033333333333333</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="K21" t="n">
         <v>9</v>
       </c>
       <c r="L21" t="n">
-        <v>108.9</v>
+        <v>108.9333333333333</v>
       </c>
       <c r="M21" t="n">
-        <v>3.914248015405401</v>
+        <v>3.268042324785212</v>
       </c>
       <c r="N21" t="n">
-        <v>0.06115492091663277</v>
+        <v>0.05116086175089199</v>
       </c>
       <c r="O21" t="n">
-        <v>0.04038656183108495</v>
+        <v>0.02711708753418903</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -6329,34 +6329,34 @@
         <v>9</v>
       </c>
       <c r="R21" t="n">
-        <v>57.93333333333333</v>
+        <v>57.96666666666667</v>
       </c>
       <c r="S21" t="n">
-        <v>5.822484964882545</v>
+        <v>3.539494619047461</v>
       </c>
       <c r="T21" t="n">
-        <v>0.06338958321325802</v>
+        <v>0.05140990238962902</v>
       </c>
       <c r="U21" t="n">
-        <v>0.05310309953766027</v>
+        <v>0.03546025533046333</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X21" t="n">
-        <v>56.13333333333333</v>
+        <v>56.26666666666667</v>
       </c>
       <c r="Y21" t="n">
-        <v>4.13731992394233</v>
+        <v>3.198619681244567</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.04065617360470054</v>
+        <v>0.03328242139806283</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.0218648507868121</v>
+        <v>0.01954160797538084</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -6365,19 +6365,19 @@
         <v>9</v>
       </c>
       <c r="AD21" t="n">
-        <v>76.76666666666667</v>
+        <v>76.83333333333333</v>
       </c>
       <c r="AE21" t="n">
-        <v>27.99193794089461</v>
+        <v>19.906630868876</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.05275885932731406</v>
+        <v>0.04183331913424093</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.03115490131584742</v>
+        <v>0.02381934998643787</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.033333333333333</v>
+        <v>3.2</v>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
@@ -6416,64 +6416,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>46.46017699115044</v>
+        <v>38.671875</v>
       </c>
       <c r="C22" t="n">
-        <v>53.53982300884955</v>
+        <v>61.32812500000001</v>
       </c>
       <c r="D22" t="n">
-        <v>7.533333333333333</v>
+        <v>8.533333333333333</v>
       </c>
       <c r="E22" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="F22" t="n">
-        <v>4.033333333333333</v>
+        <v>5.233333333333333</v>
       </c>
       <c r="G22" t="n">
-        <v>12.39293008079897</v>
+        <v>6.983829385175525</v>
       </c>
       <c r="H22" t="n">
-        <v>0.09287755007729061</v>
+        <v>0.05689696219668751</v>
       </c>
       <c r="I22" t="n">
-        <v>0.06534156287019065</v>
+        <v>0.07697212021206393</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L22" t="n">
-        <v>71.16666666666667</v>
+        <v>71.73333333333333</v>
       </c>
       <c r="M22" t="n">
-        <v>12.5875661723429</v>
+        <v>9.016200702574228</v>
       </c>
       <c r="N22" t="n">
-        <v>0.09558089483807813</v>
+        <v>0.06101151659571136</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1109063650871765</v>
+        <v>0.05898778153782144</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.033333333333333</v>
       </c>
       <c r="Q22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R22" t="n">
-        <v>89.33333333333333</v>
+        <v>89.93333333333334</v>
       </c>
       <c r="S22" t="n">
-        <v>11.31621501050073</v>
+        <v>7.032048678474284</v>
       </c>
       <c r="T22" t="n">
-        <v>0.07422667106349647</v>
+        <v>0.05736720034356091</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1290632567795075</v>
+        <v>0.05836394322343039</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -6482,16 +6482,16 @@
         <v>21</v>
       </c>
       <c r="X22" t="n">
-        <v>88.26666666666667</v>
+        <v>86.83333333333333</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.451143687684425</v>
+        <v>4.485749213895859</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.05701456238110463</v>
+        <v>0.03681522387508912</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.09894561411638221</v>
+        <v>0.06935729243326182</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -6500,19 +6500,19 @@
         <v>17</v>
       </c>
       <c r="AD22" t="n">
-        <v>51.16666666666666</v>
+        <v>51.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>64.87072571659589</v>
+        <v>40.82372524618182</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.08454388211717428</v>
+        <v>0.07090689318324528</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.06490993594236794</v>
+        <v>0.05326571318004847</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.033333333333333</v>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
@@ -6551,64 +6551,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>22.17194570135747</v>
+        <v>17.62589928057554</v>
       </c>
       <c r="C23" t="n">
-        <v>77.82805429864254</v>
+        <v>82.37410071942446</v>
       </c>
       <c r="D23" t="n">
-        <v>7.366666666666666</v>
+        <v>9.266666666666667</v>
       </c>
       <c r="E23" t="n">
         <v>1.633333333333333</v>
       </c>
       <c r="F23" t="n">
-        <v>5.733333333333333</v>
+        <v>7.633333333333334</v>
       </c>
       <c r="G23" t="n">
-        <v>3.188439562777005</v>
+        <v>2.923263696330765</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1248423713891579</v>
+        <v>0.1260836461468758</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1880687001276979</v>
+        <v>0.1656603510436155</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L23" t="n">
-        <v>79.06666666666666</v>
+        <v>79.13333333333334</v>
       </c>
       <c r="M23" t="n">
-        <v>1.510780856614543</v>
+        <v>1.55865851825943</v>
       </c>
       <c r="N23" t="n">
-        <v>0.09133488019909658</v>
+        <v>0.107051150455643</v>
       </c>
       <c r="O23" t="n">
-        <v>0.05150059844263623</v>
+        <v>0.07699746048181974</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="R23" t="n">
-        <v>63.8</v>
+        <v>64.03333333333333</v>
       </c>
       <c r="S23" t="n">
-        <v>1.966443932628185</v>
+        <v>1.808996827780643</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1302304657435017</v>
+        <v>0.1254248483666293</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1076643815800291</v>
+        <v>0.09446657318385826</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -6617,7 +6617,7 @@
         <v>68</v>
       </c>
       <c r="X23" t="n">
-        <v>92.13333333333334</v>
+        <v>92.3</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -6632,19 +6632,19 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AD23" t="n">
-        <v>64.93333333333334</v>
+        <v>64.53333333333333</v>
       </c>
       <c r="AE23" t="n">
-        <v>70.22488523797369</v>
+        <v>62.94767157610401</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.1984075264590549</v>
+        <v>0.1936653726938733</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.08635331762944531</v>
+        <v>0.08068396580048032</v>
       </c>
       <c r="AH23" t="n">
         <v>0</v>
@@ -6686,103 +6686,103 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>94.25837320574162</v>
+        <v>94.61883408071749</v>
       </c>
       <c r="C24" t="n">
-        <v>5.741626794258373</v>
+        <v>5.381165919282511</v>
       </c>
       <c r="D24" t="n">
-        <v>6.966666666666667</v>
+        <v>7.433333333333334</v>
       </c>
       <c r="E24" t="n">
-        <v>6.566666666666666</v>
+        <v>7.033333333333333</v>
       </c>
       <c r="F24" t="n">
         <v>0.4</v>
       </c>
       <c r="G24" t="n">
-        <v>6.385891676072742</v>
+        <v>3.945066704485871</v>
       </c>
       <c r="H24" t="n">
-        <v>0.05374441097746487</v>
+        <v>0.04041915297709513</v>
       </c>
       <c r="I24" t="n">
-        <v>0.02716315616807055</v>
+        <v>0.021692828305417</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="K24" t="n">
         <v>8</v>
       </c>
       <c r="L24" t="n">
-        <v>80.8</v>
+        <v>80.73333333333333</v>
       </c>
       <c r="M24" t="n">
-        <v>5.001703691861863</v>
+        <v>3.525599809553488</v>
       </c>
       <c r="N24" t="n">
-        <v>0.04511593129044256</v>
+        <v>0.03386051642626294</v>
       </c>
       <c r="O24" t="n">
-        <v>0.02990342939757269</v>
+        <v>0.01911275231699169</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.033333333333333</v>
       </c>
       <c r="Q24" t="n">
         <v>7</v>
       </c>
       <c r="R24" t="n">
-        <v>72.33333333333333</v>
+        <v>72.3</v>
       </c>
       <c r="S24" t="n">
-        <v>3.277393414958734</v>
+        <v>2.352995940834242</v>
       </c>
       <c r="T24" t="n">
-        <v>0.06248084618577476</v>
+        <v>0.04884710455451786</v>
       </c>
       <c r="U24" t="n">
-        <v>0.03536584342583343</v>
+        <v>0.03154982935881309</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X24" t="n">
-        <v>46.66666666666666</v>
+        <v>46.7</v>
       </c>
       <c r="Y24" t="n">
-        <v>9.455216977845394</v>
+        <v>5.078175841440288</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.03075124276490824</v>
+        <v>0.02344901078474637</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.02131862380145378</v>
+        <v>0.01013613542123196</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="AC24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD24" t="n">
-        <v>100.2</v>
+        <v>100.2666666666667</v>
       </c>
       <c r="AE24" t="n">
-        <v>27.95675059725205</v>
+        <v>17.52289905075644</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.04935354200966341</v>
+        <v>0.03578345709833375</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.02276886458168792</v>
+        <v>0.01884309692464947</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
@@ -6821,28 +6821,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>71.76870748299319</v>
+        <v>68.9655172413793</v>
       </c>
       <c r="C25" t="n">
-        <v>28.2312925170068</v>
+        <v>31.03448275862069</v>
       </c>
       <c r="D25" t="n">
-        <v>9.800000000000001</v>
+        <v>10.63333333333333</v>
       </c>
       <c r="E25" t="n">
-        <v>7.033333333333333</v>
+        <v>7.333333333333333</v>
       </c>
       <c r="F25" t="n">
-        <v>2.766666666666667</v>
+        <v>3.3</v>
       </c>
       <c r="G25" t="n">
-        <v>9.851287654499139</v>
+        <v>8.981546043150868</v>
       </c>
       <c r="H25" t="n">
-        <v>0.04623353356170176</v>
+        <v>0.04446781123497526</v>
       </c>
       <c r="I25" t="n">
-        <v>0.02497993844920491</v>
+        <v>0.02231588105157622</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -6851,16 +6851,16 @@
         <v>11</v>
       </c>
       <c r="L25" t="n">
-        <v>148.0666666666667</v>
+        <v>148.1666666666667</v>
       </c>
       <c r="M25" t="n">
-        <v>7.090882301012156</v>
+        <v>4.142136131235076</v>
       </c>
       <c r="N25" t="n">
-        <v>0.07853229027387357</v>
+        <v>0.07100048323772211</v>
       </c>
       <c r="O25" t="n">
-        <v>0.05480722481773916</v>
+        <v>0.04917966814872365</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -6869,16 +6869,16 @@
         <v>10</v>
       </c>
       <c r="R25" t="n">
-        <v>60.73333333333333</v>
+        <v>60.76666666666667</v>
       </c>
       <c r="S25" t="n">
-        <v>4.128918374561321</v>
+        <v>3.908801806346149</v>
       </c>
       <c r="T25" t="n">
-        <v>0.07239990344062154</v>
+        <v>0.07277748239780306</v>
       </c>
       <c r="U25" t="n">
-        <v>0.06091234701368249</v>
+        <v>0.05354368762876972</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -6887,16 +6887,16 @@
         <v>8</v>
       </c>
       <c r="X25" t="n">
-        <v>47</v>
+        <v>46.83333333333334</v>
       </c>
       <c r="Y25" t="n">
-        <v>3.945385486706481</v>
+        <v>2.926665785840691</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.05480605278755394</v>
+        <v>0.04983551526549825</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.04582306405646133</v>
+        <v>0.03291786720137163</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -6905,16 +6905,16 @@
         <v>6</v>
       </c>
       <c r="AD25" t="n">
-        <v>44.13333333333333</v>
+        <v>44.23333333333333</v>
       </c>
       <c r="AE25" t="n">
-        <v>27.63975946979243</v>
+        <v>22.29356503570732</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.06225547396527439</v>
+        <v>0.0597866128245334</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.03033161563356007</v>
+        <v>0.02899487412437662</v>
       </c>
       <c r="AH25" t="n">
         <v>0</v>
@@ -7277,61 +7277,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.7987012987013</v>
+        <v>14.05622489959839</v>
       </c>
       <c r="C4" t="n">
-        <v>28.4090909090909</v>
+        <v>28.19277108433735</v>
       </c>
       <c r="D4" t="n">
-        <v>34.00974025974026</v>
+        <v>33.73493975903614</v>
       </c>
       <c r="E4" t="n">
-        <v>23.78246753246753</v>
+        <v>24.01606425702811</v>
       </c>
       <c r="F4" t="n">
-        <v>41.06666666666667</v>
+        <v>41.5</v>
       </c>
       <c r="G4" t="n">
-        <v>5.666666666666667</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="H4" t="n">
-        <v>11.66666666666667</v>
+        <v>11.7</v>
       </c>
       <c r="I4" t="n">
-        <v>13.96666666666667</v>
+        <v>14</v>
       </c>
       <c r="J4" t="n">
-        <v>9.766666666666667</v>
+        <v>9.966666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>8.187201505185861</v>
+        <v>8.172062719653663</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03003352156893662</v>
+        <v>0.02990167982153789</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01586062959007869</v>
+        <v>0.0166334466245786</v>
       </c>
       <c r="N4" t="n">
-        <v>1.033333333333333</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="O4" t="n">
         <v>13</v>
       </c>
       <c r="P4" t="n">
-        <v>208.2</v>
+        <v>208.2333333333333</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.052480655160704</v>
+        <v>5.895828075041655</v>
       </c>
       <c r="R4" t="n">
-        <v>0.04027831791764497</v>
+        <v>0.03999406622458723</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02985879818794954</v>
+        <v>0.02850368265778115</v>
       </c>
       <c r="T4" t="n">
-        <v>1.166666666666667</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="U4" t="n">
         <v>10</v>
@@ -7340,16 +7340,16 @@
         <v>100.9666666666667</v>
       </c>
       <c r="W4" t="n">
-        <v>7.138473315495614</v>
+        <v>7.040187041575411</v>
       </c>
       <c r="X4" t="n">
-        <v>0.02641357467413251</v>
+        <v>0.02629467406097513</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01554572285333681</v>
+        <v>0.01606801987542305</v>
       </c>
       <c r="Z4" t="n">
-        <v>13.96666666666667</v>
+        <v>21.86666666666667</v>
       </c>
       <c r="AA4" t="n">
         <v>13</v>
@@ -7358,34 +7358,34 @@
         <v>178.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.15514666864171</v>
+        <v>6.085593535037626</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.03804866010851636</v>
+        <v>0.03773207456915185</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.02878166774119143</v>
+        <v>0.02886545428778536</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.1</v>
+        <v>3.266666666666667</v>
       </c>
       <c r="AG4" t="n">
         <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>112.5333333333333</v>
+        <v>112.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>30.2174405652812</v>
+        <v>29.82164467726397</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.02838604703397798</v>
+        <v>0.02768997965524309</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.01340654020256737</v>
+        <v>0.0140507530244931</v>
       </c>
       <c r="AL4" t="n">
-        <v>18.26666666666667</v>
+        <v>30.46666666666667</v>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
@@ -7424,58 +7424,58 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.56839422259983</v>
+        <v>3.373493975903615</v>
       </c>
       <c r="C5" t="n">
-        <v>18.69158878504673</v>
+        <v>20.88353413654619</v>
       </c>
       <c r="D5" t="n">
-        <v>43.33050127442651</v>
+        <v>43.69477911646586</v>
       </c>
       <c r="E5" t="n">
-        <v>34.40951571792693</v>
+        <v>32.04819277108434</v>
       </c>
       <c r="F5" t="n">
-        <v>39.23333333333333</v>
+        <v>41.5</v>
       </c>
       <c r="G5" t="n">
         <v>1.4</v>
       </c>
       <c r="H5" t="n">
-        <v>7.333333333333333</v>
+        <v>8.666666666666666</v>
       </c>
       <c r="I5" t="n">
-        <v>17</v>
+        <v>18.13333333333333</v>
       </c>
       <c r="J5" t="n">
-        <v>13.5</v>
+        <v>13.3</v>
       </c>
       <c r="K5" t="n">
-        <v>6.828076214000627</v>
+        <v>4.014769066372567</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06555531401760022</v>
+        <v>0.05942886624758703</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04484844899690687</v>
+        <v>0.0372984374036556</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.066666666666667</v>
       </c>
       <c r="O5" t="n">
         <v>8</v>
       </c>
       <c r="P5" t="n">
-        <v>63.06666666666667</v>
+        <v>63.46666666666667</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.045203881183015</v>
+        <v>1.956389933920025</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0591701559710669</v>
+        <v>0.05839134840115717</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04815837663577205</v>
+        <v>0.04957380939500645</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -7484,55 +7484,55 @@
         <v>8</v>
       </c>
       <c r="V5" t="n">
-        <v>35.9</v>
+        <v>35.73333333333333</v>
       </c>
       <c r="W5" t="n">
-        <v>14.6555175429969</v>
+        <v>13.19769581645564</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02707408698225812</v>
+        <v>0.02659770216695179</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01852576606318309</v>
+        <v>0.01643276189683782</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.066666666666667</v>
+        <v>10.53333333333333</v>
       </c>
       <c r="AA5" t="n">
         <v>19</v>
       </c>
       <c r="AB5" t="n">
-        <v>355.7</v>
+        <v>356.0333333333334</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.499263825560218</v>
+        <v>6.892028306429681</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.04154574470509496</v>
+        <v>0.04017009364298212</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.01640192546511389</v>
+        <v>0.01728021279523967</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="AG5" t="n">
         <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>145.0666666666667</v>
+        <v>144.7666666666667</v>
       </c>
       <c r="AI5" t="n">
-        <v>33.68464999534286</v>
+        <v>28.56582162103575</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.03271051705264671</v>
+        <v>0.03121564144209915</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.01660384498225254</v>
+        <v>0.01567213619430818</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.066666666666667</v>
+        <v>13.66666666666667</v>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
@@ -7571,58 +7571,58 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.08340888485948</v>
+        <v>35.28384279475983</v>
       </c>
       <c r="C6" t="n">
-        <v>6.708975521305531</v>
+        <v>7.423580786026203</v>
       </c>
       <c r="D6" t="n">
-        <v>12.14868540344515</v>
+        <v>11.96506550218341</v>
       </c>
       <c r="E6" t="n">
-        <v>45.05893019038985</v>
+        <v>45.32751091703057</v>
       </c>
       <c r="F6" t="n">
-        <v>36.76666666666667</v>
+        <v>38.16666666666666</v>
       </c>
       <c r="G6" t="n">
-        <v>13.26666666666667</v>
+        <v>13.46666666666667</v>
       </c>
       <c r="H6" t="n">
-        <v>2.466666666666667</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="I6" t="n">
-        <v>4.466666666666667</v>
+        <v>4.566666666666666</v>
       </c>
       <c r="J6" t="n">
-        <v>16.56666666666667</v>
+        <v>17.3</v>
       </c>
       <c r="K6" t="n">
-        <v>14.41032792370952</v>
+        <v>9.308797509356976</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0353486564603533</v>
+        <v>0.02744673770677674</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01725892058045577</v>
+        <v>0.01385243550639987</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.233333333333333</v>
       </c>
       <c r="O6" t="n">
         <v>15</v>
       </c>
       <c r="P6" t="n">
-        <v>286.0666666666667</v>
+        <v>286.3666666666667</v>
       </c>
       <c r="Q6" t="n">
-        <v>15.25417355601635</v>
+        <v>7.871646417451981</v>
       </c>
       <c r="R6" t="n">
-        <v>0.06927517343914238</v>
+        <v>0.05264649253474552</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0471210314509312</v>
+        <v>0.03345590665149992</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -7631,16 +7631,16 @@
         <v>24</v>
       </c>
       <c r="V6" t="n">
-        <v>134.4333333333333</v>
+        <v>134.3333333333333</v>
       </c>
       <c r="W6" t="n">
-        <v>3.085590807896697</v>
+        <v>2.741415792123549</v>
       </c>
       <c r="X6" t="n">
-        <v>0.07850180734822336</v>
+        <v>0.07425506136426004</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.04668869751199081</v>
+        <v>0.04097619084534296</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -7649,16 +7649,16 @@
         <v>13</v>
       </c>
       <c r="AB6" t="n">
-        <v>43.6</v>
+        <v>43.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.711462587670098</v>
+        <v>6.375623395573438</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.04957099399329446</v>
+        <v>0.04231391351591973</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.03478458243993865</v>
+        <v>0.02899113144146109</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -7667,19 +7667,19 @@
         <v>20</v>
       </c>
       <c r="AH6" t="n">
-        <v>135.1</v>
+        <v>135.4333333333333</v>
       </c>
       <c r="AI6" t="n">
-        <v>52.74352854066792</v>
+        <v>35.14031976989389</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.04779092530777912</v>
+        <v>0.03793624183481026</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.02358828937040719</v>
+        <v>0.01859685776722236</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>3.233333333333333</v>
       </c>
       <c r="AM6" t="n">
         <v>385</v>
@@ -7716,115 +7716,115 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>44.17372881355932</v>
+        <v>42.71356783919598</v>
       </c>
       <c r="C7" t="n">
-        <v>15.99576271186441</v>
+        <v>16.28140703517588</v>
       </c>
       <c r="D7" t="n">
-        <v>20.44491525423729</v>
+        <v>21.20603015075377</v>
       </c>
       <c r="E7" t="n">
-        <v>19.38559322033898</v>
+        <v>19.79899497487437</v>
       </c>
       <c r="F7" t="n">
-        <v>31.46666666666667</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="G7" t="n">
-        <v>13.9</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="H7" t="n">
-        <v>5.033333333333333</v>
+        <v>5.4</v>
       </c>
       <c r="I7" t="n">
-        <v>6.433333333333334</v>
+        <v>7.033333333333333</v>
       </c>
       <c r="J7" t="n">
-        <v>6.1</v>
+        <v>6.566666666666666</v>
       </c>
       <c r="K7" t="n">
-        <v>8.451034505520209</v>
+        <v>6.958773152266376</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08090364929593004</v>
+        <v>0.07264868275657579</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05767529148471406</v>
+        <v>0.05090196653408582</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.033333333333333</v>
       </c>
       <c r="O7" t="n">
         <v>15</v>
       </c>
       <c r="P7" t="n">
-        <v>88.03333333333333</v>
+        <v>88.06666666666666</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.71804697015145</v>
+        <v>5.385715520279915</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0796030259777098</v>
+        <v>0.05764109279052473</v>
       </c>
       <c r="S7" t="n">
-        <v>0.05472396796556824</v>
+        <v>0.04433537597755223</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="V7" t="n">
-        <v>80.90000000000001</v>
+        <v>81.76666666666667</v>
       </c>
       <c r="W7" t="n">
-        <v>10.51785419743966</v>
+        <v>7.25775649402862</v>
       </c>
       <c r="X7" t="n">
-        <v>0.07055605340310084</v>
+        <v>0.05247183280186411</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.05081644434323683</v>
+        <v>0.03070558411312595</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA7" t="n">
         <v>14</v>
       </c>
       <c r="AB7" t="n">
-        <v>103</v>
+        <v>102.6666666666667</v>
       </c>
       <c r="AC7" t="n">
-        <v>14.79663197526663</v>
+        <v>10.2687647884388</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.03126837619901131</v>
+        <v>0.0244697187605694</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.01722326006739835</v>
+        <v>0.01330534129532686</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="AG7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
-        <v>327.4</v>
+        <v>327.4333333333333</v>
       </c>
       <c r="AI7" t="n">
-        <v>54.04129616980466</v>
+        <v>33.578538744842</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.04728772166333797</v>
+        <v>0.03535941853588401</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.02268955262202688</v>
+        <v>0.01666109740946553</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>7.466666666666667</v>
       </c>
       <c r="AM7" t="n">
         <v>385</v>
@@ -7861,58 +7861,58 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24.23371647509579</v>
+        <v>23.26869806094183</v>
       </c>
       <c r="C8" t="n">
-        <v>28.35249042145594</v>
+        <v>31.11726685133887</v>
       </c>
       <c r="D8" t="n">
-        <v>34.57854406130268</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="E8" t="n">
-        <v>12.83524904214559</v>
+        <v>12.28070175438597</v>
       </c>
       <c r="F8" t="n">
-        <v>34.8</v>
+        <v>36.1</v>
       </c>
       <c r="G8" t="n">
-        <v>8.433333333333334</v>
+        <v>8.4</v>
       </c>
       <c r="H8" t="n">
-        <v>9.866666666666667</v>
+        <v>11.23333333333333</v>
       </c>
       <c r="I8" t="n">
         <v>12.03333333333333</v>
       </c>
       <c r="J8" t="n">
-        <v>4.466666666666667</v>
+        <v>4.433333333333334</v>
       </c>
       <c r="K8" t="n">
-        <v>11.95716695757794</v>
+        <v>8.065454185066864</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05339444269738317</v>
+        <v>0.04628608716465109</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03661221422681362</v>
+        <v>0.0294053974943607</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P8" t="n">
-        <v>134.1</v>
+        <v>134.5333333333333</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.539569440601218</v>
+        <v>7.547581468630201</v>
       </c>
       <c r="R8" t="n">
-        <v>0.04007593825660143</v>
+        <v>0.03659934726016198</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02288802596016049</v>
+        <v>0.0194555223413105</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -7921,34 +7921,34 @@
         <v>11</v>
       </c>
       <c r="V8" t="n">
-        <v>175.5333333333333</v>
+        <v>175.1</v>
       </c>
       <c r="W8" t="n">
-        <v>11.07369281439655</v>
+        <v>10.50892485778665</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0489794101280675</v>
+        <v>0.04667627922717628</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0339774277361667</v>
+        <v>0.03399475282520018</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB8" t="n">
-        <v>164.9333333333333</v>
+        <v>165.0333333333333</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.687322323674215</v>
+        <v>5.531252477017743</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.03592431251776874</v>
+        <v>0.03489440763569064</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0239816297025495</v>
+        <v>0.02680918673964798</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -7957,16 +7957,16 @@
         <v>15</v>
       </c>
       <c r="AH8" t="n">
-        <v>125.3666666666667</v>
+        <v>125.3333333333333</v>
       </c>
       <c r="AI8" t="n">
-        <v>41.25206899012186</v>
+        <v>35.45796159082977</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.04126959991305951</v>
+        <v>0.03897921887221362</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.02247772718314411</v>
+        <v>0.02151762039941418</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -8008,40 +8008,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.706984667802385</v>
+        <v>5.602006688963211</v>
       </c>
       <c r="C9" t="n">
-        <v>28.44974446337308</v>
+        <v>28.34448160535117</v>
       </c>
       <c r="D9" t="n">
-        <v>49.48892674616695</v>
+        <v>49.91638795986621</v>
       </c>
       <c r="E9" t="n">
-        <v>16.35434412265758</v>
+        <v>16.1371237458194</v>
       </c>
       <c r="F9" t="n">
-        <v>39.13333333333333</v>
+        <v>39.86666666666667</v>
       </c>
       <c r="G9" t="n">
         <v>2.233333333333333</v>
       </c>
       <c r="H9" t="n">
-        <v>11.13333333333333</v>
+        <v>11.3</v>
       </c>
       <c r="I9" t="n">
-        <v>19.36666666666667</v>
+        <v>19.9</v>
       </c>
       <c r="J9" t="n">
-        <v>6.4</v>
+        <v>6.433333333333334</v>
       </c>
       <c r="K9" t="n">
-        <v>12.51673960245874</v>
+        <v>10.62091449716856</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05914304887593896</v>
+        <v>0.05388745340505927</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02740112591057138</v>
+        <v>0.02795325160665788</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -8050,16 +8050,16 @@
         <v>23</v>
       </c>
       <c r="P9" t="n">
-        <v>186.0666666666667</v>
+        <v>186.2666666666667</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.724957076364186</v>
+        <v>4.403436816010663</v>
       </c>
       <c r="R9" t="n">
-        <v>0.05915229899656815</v>
+        <v>0.054614880614314</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03753351694886544</v>
+        <v>0.03454246773674512</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -8068,34 +8068,34 @@
         <v>15</v>
       </c>
       <c r="V9" t="n">
-        <v>80.83333333333333</v>
+        <v>80.56666666666666</v>
       </c>
       <c r="W9" t="n">
-        <v>13.88181562494138</v>
+        <v>12.77934635598155</v>
       </c>
       <c r="X9" t="n">
-        <v>0.04515007194799216</v>
+        <v>0.04330148246722732</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.02681512039124233</v>
+        <v>0.02468973531939786</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.033333333333333</v>
       </c>
       <c r="AA9" t="n">
         <v>19</v>
       </c>
       <c r="AB9" t="n">
-        <v>248.8333333333333</v>
+        <v>248.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.439369501004103</v>
+        <v>5.052460126801474</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.05556943922459539</v>
+        <v>0.053468843550916</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.02716902209781423</v>
+        <v>0.02729291915527765</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -8104,19 +8104,19 @@
         <v>11</v>
       </c>
       <c r="AH9" t="n">
-        <v>84.26666666666667</v>
+        <v>84.36666666666666</v>
       </c>
       <c r="AI9" t="n">
-        <v>41.94068931095217</v>
+        <v>37.8615750543407</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.05188168959609807</v>
+        <v>0.04837229974460061</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.02760598161381805</v>
+        <v>0.0248558994749275</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.033333333333333</v>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
@@ -8155,40 +8155,40 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12.12415130940834</v>
+        <v>11.73570019723866</v>
       </c>
       <c r="C10" t="n">
-        <v>45.97478176527643</v>
+        <v>44.18145956607495</v>
       </c>
       <c r="D10" t="n">
-        <v>16.10087293889428</v>
+        <v>17.94871794871795</v>
       </c>
       <c r="E10" t="n">
-        <v>25.80019398642095</v>
+        <v>26.13412228796845</v>
       </c>
       <c r="F10" t="n">
-        <v>34.36666666666667</v>
+        <v>33.8</v>
       </c>
       <c r="G10" t="n">
-        <v>4.166666666666667</v>
+        <v>3.966666666666667</v>
       </c>
       <c r="H10" t="n">
-        <v>15.8</v>
+        <v>14.93333333333333</v>
       </c>
       <c r="I10" t="n">
-        <v>5.533333333333333</v>
+        <v>6.066666666666666</v>
       </c>
       <c r="J10" t="n">
-        <v>8.866666666666667</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K10" t="n">
-        <v>6.65896014160821</v>
+        <v>6.194409870513811</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03708299656015399</v>
+        <v>0.03688393986554418</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02389431841433048</v>
+        <v>0.0182558790831733</v>
       </c>
       <c r="N10" t="n">
         <v>1.033333333333333</v>
@@ -8197,34 +8197,34 @@
         <v>12</v>
       </c>
       <c r="P10" t="n">
-        <v>134.9</v>
+        <v>134.9666666666667</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.816206658506614</v>
+        <v>6.419305654595986</v>
       </c>
       <c r="R10" t="n">
-        <v>0.02493166282576305</v>
+        <v>0.02482002295177509</v>
       </c>
       <c r="S10" t="n">
-        <v>0.011297556579619</v>
+        <v>0.01157873763095249</v>
       </c>
       <c r="T10" t="n">
-        <v>3.266666666666667</v>
+        <v>3.2</v>
       </c>
       <c r="U10" t="n">
         <v>10</v>
       </c>
       <c r="V10" t="n">
-        <v>210.2666666666667</v>
+        <v>210.3</v>
       </c>
       <c r="W10" t="n">
-        <v>6.969358043154124</v>
+        <v>6.882620597320413</v>
       </c>
       <c r="X10" t="n">
-        <v>0.02962164940695021</v>
+        <v>0.02969557123546731</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.01538628643719601</v>
+        <v>0.01524888108578925</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -8233,16 +8233,16 @@
         <v>12</v>
       </c>
       <c r="AB10" t="n">
-        <v>155.5</v>
+        <v>155.4333333333333</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.240148360819591</v>
+        <v>4.322879841143385</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.04127835009925841</v>
+        <v>0.04269458323175866</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.02596285147696994</v>
+        <v>0.02741063683514609</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -8251,19 +8251,19 @@
         <v>12</v>
       </c>
       <c r="AH10" t="n">
-        <v>99.33333333333333</v>
+        <v>99.3</v>
       </c>
       <c r="AI10" t="n">
-        <v>27.93776874828173</v>
+        <v>27.09859779322308</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.03035525924600047</v>
+        <v>0.0307143771021339</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.01335724414467054</v>
+        <v>0.01314125807774646</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.3</v>
+        <v>4.233333333333333</v>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
@@ -8302,58 +8302,58 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10.48951048951049</v>
+        <v>10.22727272727273</v>
       </c>
       <c r="C11" t="n">
-        <v>19.6439923712651</v>
+        <v>20.26515151515152</v>
       </c>
       <c r="D11" t="n">
-        <v>38.97012078830261</v>
+        <v>38.51010101010101</v>
       </c>
       <c r="E11" t="n">
-        <v>30.89637635092181</v>
+        <v>30.99747474747475</v>
       </c>
       <c r="F11" t="n">
-        <v>52.43333333333333</v>
+        <v>52.8</v>
       </c>
       <c r="G11" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H11" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="I11" t="n">
-        <v>20.43333333333333</v>
+        <v>20.33333333333333</v>
       </c>
       <c r="J11" t="n">
-        <v>16.2</v>
+        <v>16.36666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>5.98345632316342</v>
+        <v>4.375357999934321</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04392239140012384</v>
+        <v>0.03742418620204433</v>
       </c>
       <c r="M11" t="n">
-        <v>0.027641630269419</v>
+        <v>0.01608926673634645</v>
       </c>
       <c r="N11" t="n">
-        <v>1.033333333333333</v>
+        <v>6.433333333333334</v>
       </c>
       <c r="O11" t="n">
         <v>7</v>
       </c>
       <c r="P11" t="n">
-        <v>89.33333333333333</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.389401706860551</v>
+        <v>2.271807476135968</v>
       </c>
       <c r="R11" t="n">
-        <v>0.04877804460928233</v>
+        <v>0.04478091733844016</v>
       </c>
       <c r="S11" t="n">
-        <v>0.02945914853385645</v>
+        <v>0.02800069456206602</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -8362,37 +8362,37 @@
         <v>8</v>
       </c>
       <c r="V11" t="n">
-        <v>41.33333333333334</v>
+        <v>41.16666666666666</v>
       </c>
       <c r="W11" t="n">
-        <v>15.63195891057284</v>
+        <v>12.08229422206303</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01901472045919102</v>
+        <v>0.01617799996579904</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.01110226219306875</v>
+        <v>0.008739593354854944</v>
       </c>
       <c r="Z11" t="n">
-        <v>7.366666666666667</v>
+        <v>32.43333333333334</v>
       </c>
       <c r="AA11" t="n">
         <v>8</v>
       </c>
       <c r="AB11" t="n">
-        <v>362.5666666666667</v>
+        <v>362.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.421393294461716</v>
+        <v>4.366548019376811</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.03051182282786771</v>
+        <v>0.02756518025237441</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.01746308315518799</v>
+        <v>0.01563874168135689</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AG11" t="n">
         <v>7</v>
@@ -8401,16 +8401,16 @@
         <v>106.7333333333333</v>
       </c>
       <c r="AI11" t="n">
-        <v>30.18518361001133</v>
+        <v>23.68857117578331</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.02460225922930903</v>
+        <v>0.02066421435336774</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.0113172617868903</v>
+        <v>0.0100571055076385</v>
       </c>
       <c r="AL11" t="n">
-        <v>8.4</v>
+        <v>43.26666666666667</v>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
@@ -8449,40 +8449,40 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30.83235638921454</v>
+        <v>31.34328358208955</v>
       </c>
       <c r="C12" t="n">
-        <v>21.68815943728019</v>
+        <v>21.01033295063146</v>
       </c>
       <c r="D12" t="n">
-        <v>21.45369284876905</v>
+        <v>21.46957520091848</v>
       </c>
       <c r="E12" t="n">
-        <v>26.02579132473623</v>
+        <v>26.1768082663605</v>
       </c>
       <c r="F12" t="n">
-        <v>28.43333333333333</v>
+        <v>29.03333333333333</v>
       </c>
       <c r="G12" t="n">
-        <v>8.766666666666667</v>
+        <v>9.1</v>
       </c>
       <c r="H12" t="n">
-        <v>6.166666666666667</v>
+        <v>6.1</v>
       </c>
       <c r="I12" t="n">
-        <v>6.1</v>
+        <v>6.233333333333333</v>
       </c>
       <c r="J12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="K12" t="n">
-        <v>12.37066261672462</v>
+        <v>9.310655377207864</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04738531867549816</v>
+        <v>0.03579143698693615</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0195116273412559</v>
+        <v>0.01354057223744039</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -8491,16 +8491,16 @@
         <v>20</v>
       </c>
       <c r="P12" t="n">
-        <v>256.0666666666667</v>
+        <v>255.9666666666667</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.550266699178434</v>
+        <v>4.797856594179018</v>
       </c>
       <c r="R12" t="n">
-        <v>0.05809269248593479</v>
+        <v>0.05041506847285804</v>
       </c>
       <c r="S12" t="n">
-        <v>0.04172987497593576</v>
+        <v>0.03455254395676221</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -8509,16 +8509,16 @@
         <v>26</v>
       </c>
       <c r="V12" t="n">
-        <v>101.8666666666667</v>
+        <v>101.9666666666667</v>
       </c>
       <c r="W12" t="n">
-        <v>7.041477897420254</v>
+        <v>4.280678463737468</v>
       </c>
       <c r="X12" t="n">
-        <v>0.05533676250354128</v>
+        <v>0.04412044367116278</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.04371644748003746</v>
+        <v>0.02987258191139462</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -8527,16 +8527,16 @@
         <v>21</v>
       </c>
       <c r="AB12" t="n">
-        <v>78.3</v>
+        <v>78.36666666666666</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.777876228977304</v>
+        <v>8.213772364136446</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.06052523908799693</v>
+        <v>0.05117395153065291</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.03688824146077844</v>
+        <v>0.02863074657788465</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -8545,16 +8545,16 @@
         <v>28</v>
       </c>
       <c r="AH12" t="n">
-        <v>163.5</v>
+        <v>163.6333333333333</v>
       </c>
       <c r="AI12" t="n">
-        <v>54.2690460361116</v>
+        <v>41.16950627935471</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.0543519830482676</v>
+        <v>0.04329174676164366</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.02400772351679442</v>
+        <v>0.02043391901275071</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -8594,115 +8594,115 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24.76038338658147</v>
+        <v>26.34730538922156</v>
       </c>
       <c r="C13" t="n">
-        <v>16.93290734824281</v>
+        <v>17.51497005988024</v>
       </c>
       <c r="D13" t="n">
-        <v>27.31629392971246</v>
+        <v>25.44910179640719</v>
       </c>
       <c r="E13" t="n">
-        <v>30.99041533546326</v>
+        <v>30.68862275449101</v>
       </c>
       <c r="F13" t="n">
-        <v>20.86666666666667</v>
+        <v>22.26666666666667</v>
       </c>
       <c r="G13" t="n">
-        <v>5.166666666666667</v>
+        <v>5.866666666666666</v>
       </c>
       <c r="H13" t="n">
-        <v>3.533333333333333</v>
+        <v>3.9</v>
       </c>
       <c r="I13" t="n">
-        <v>5.7</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="J13" t="n">
-        <v>6.466666666666667</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>12.28310451933715</v>
+        <v>7.099001101735422</v>
       </c>
       <c r="L13" t="n">
-        <v>0.07667151570545527</v>
+        <v>0.05685425569226334</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0969683228212416</v>
+        <v>0.03611146759278832</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P13" t="n">
-        <v>89.2</v>
+        <v>88.93333333333334</v>
       </c>
       <c r="Q13" t="n">
-        <v>14.62588295977463</v>
+        <v>4.222702518018868</v>
       </c>
       <c r="R13" t="n">
-        <v>0.07770604412054721</v>
+        <v>0.06339831423143261</v>
       </c>
       <c r="S13" t="n">
-        <v>0.09787251057125894</v>
+        <v>0.0274441939952923</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="U13" t="n">
         <v>11</v>
       </c>
       <c r="V13" t="n">
-        <v>110.0333333333333</v>
+        <v>110.4</v>
       </c>
       <c r="W13" t="n">
-        <v>18.52405000902793</v>
+        <v>10.08684842162204</v>
       </c>
       <c r="X13" t="n">
-        <v>0.03161169945779418</v>
+        <v>0.02343585340929126</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.02017822972494727</v>
+        <v>0.01508425393027739</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.133333333333333</v>
       </c>
       <c r="AA13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>288.8333333333333</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>6.275041953438502</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.04905557108451205</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.02766216192370713</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
         <v>10</v>
       </c>
-      <c r="AB13" t="n">
-        <v>288.6666666666667</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>14.9300458717759</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0.05963381283240936</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0.0311130115837901</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>11</v>
-      </c>
       <c r="AH13" t="n">
-        <v>111.1</v>
+        <v>111.8</v>
       </c>
       <c r="AI13" t="n">
-        <v>71.24727118339257</v>
+        <v>31.29803817438543</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.03892810919936465</v>
+        <v>0.03064922328168196</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.01819328481377602</v>
+        <v>0.01490826840919823</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>4.266666666666667</v>
       </c>
       <c r="AM13" t="n">
         <v>385</v>
@@ -8739,58 +8739,58 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19.23641703377386</v>
+        <v>20.93683463449255</v>
       </c>
       <c r="C14" t="n">
-        <v>25.69750367107195</v>
+        <v>25.47906316536551</v>
       </c>
       <c r="D14" t="n">
-        <v>35.38913362701909</v>
+        <v>33.78282469836763</v>
       </c>
       <c r="E14" t="n">
-        <v>19.6769456681351</v>
+        <v>19.80127750177431</v>
       </c>
       <c r="F14" t="n">
-        <v>45.4</v>
+        <v>46.96666666666667</v>
       </c>
       <c r="G14" t="n">
-        <v>8.733333333333333</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="H14" t="n">
-        <v>11.66666666666667</v>
+        <v>11.96666666666667</v>
       </c>
       <c r="I14" t="n">
-        <v>16.06666666666667</v>
+        <v>15.86666666666667</v>
       </c>
       <c r="J14" t="n">
-        <v>8.933333333333334</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>13.15302127752103</v>
+        <v>9.267865302754364</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05604962242544381</v>
+        <v>0.04670241016238821</v>
       </c>
       <c r="M14" t="n">
-        <v>0.04247287741570237</v>
+        <v>0.03057987625669262</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P14" t="n">
-        <v>137.0666666666667</v>
+        <v>137.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>12.01111052285605</v>
+        <v>9.553885038162781</v>
       </c>
       <c r="R14" t="n">
-        <v>0.05785484795029447</v>
+        <v>0.05444421865021291</v>
       </c>
       <c r="S14" t="n">
-        <v>0.03628156147473875</v>
+        <v>0.0333640630377918</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -8799,16 +8799,16 @@
         <v>15</v>
       </c>
       <c r="V14" t="n">
-        <v>141.4</v>
+        <v>141.6666666666667</v>
       </c>
       <c r="W14" t="n">
-        <v>17.24187176544235</v>
+        <v>8.809237666787286</v>
       </c>
       <c r="X14" t="n">
-        <v>0.06438901757646762</v>
+        <v>0.05108527890314195</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.03400473495987349</v>
+        <v>0.02628374157554499</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -8817,16 +8817,16 @@
         <v>20</v>
       </c>
       <c r="AB14" t="n">
-        <v>142.6333333333333</v>
+        <v>142.8333333333333</v>
       </c>
       <c r="AC14" t="n">
-        <v>14.57706241957134</v>
+        <v>10.73848492508665</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.06091450126513519</v>
+        <v>0.05308903620856302</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.04057977493731822</v>
+        <v>0.03417956402359974</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -8838,13 +8838,13 @@
         <v>178.2666666666667</v>
       </c>
       <c r="AI14" t="n">
-        <v>61.02378500487389</v>
+        <v>42.30634629428741</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.06175937864608305</v>
+        <v>0.05162387496998727</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.03595205681197844</v>
+        <v>0.02967899867328294</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -8884,115 +8884,115 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.742782152230971</v>
+        <v>8.010012515644556</v>
       </c>
       <c r="C15" t="n">
-        <v>17.71653543307087</v>
+        <v>18.02252816020025</v>
       </c>
       <c r="D15" t="n">
-        <v>44.2257217847769</v>
+        <v>43.67959949937421</v>
       </c>
       <c r="E15" t="n">
-        <v>30.31496062992126</v>
+        <v>30.28785982478098</v>
       </c>
       <c r="F15" t="n">
-        <v>25.4</v>
+        <v>26.63333333333333</v>
       </c>
       <c r="G15" t="n">
-        <v>1.966666666666667</v>
+        <v>2.133333333333333</v>
       </c>
       <c r="H15" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="I15" t="n">
-        <v>11.23333333333333</v>
+        <v>11.63333333333333</v>
       </c>
       <c r="J15" t="n">
-        <v>7.7</v>
+        <v>8.066666666666666</v>
       </c>
       <c r="K15" t="n">
-        <v>12.9015324807033</v>
+        <v>6.460830191935386</v>
       </c>
       <c r="L15" t="n">
-        <v>0.06073040858869326</v>
+        <v>0.04391746658981038</v>
       </c>
       <c r="M15" t="n">
-        <v>0.03280076200387754</v>
+        <v>0.02547564819730955</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.266666666666667</v>
       </c>
       <c r="O15" t="n">
         <v>16</v>
       </c>
       <c r="P15" t="n">
-        <v>136.9666666666667</v>
+        <v>137.0333333333333</v>
       </c>
       <c r="Q15" t="n">
-        <v>21.81216206117917</v>
+        <v>6.647065952310728</v>
       </c>
       <c r="R15" t="n">
-        <v>0.06708655695616295</v>
+        <v>0.04040778446709178</v>
       </c>
       <c r="S15" t="n">
-        <v>0.04861323114495975</v>
+        <v>0.0204598517672776</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U15" t="n">
         <v>15</v>
       </c>
       <c r="V15" t="n">
-        <v>119.8</v>
+        <v>120</v>
       </c>
       <c r="W15" t="n">
-        <v>27.84638701025002</v>
+        <v>9.317313442060815</v>
       </c>
       <c r="X15" t="n">
-        <v>0.04623849654929236</v>
+        <v>0.02121328587237638</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.03237791848906917</v>
+        <v>0.01458512787586867</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.066666666666667</v>
+        <v>21.73333333333333</v>
       </c>
       <c r="AA15" t="n">
         <v>15</v>
       </c>
       <c r="AB15" t="n">
-        <v>252.7666666666667</v>
+        <v>252.8666666666667</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.088083815262266</v>
+        <v>4.817052514745022</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.06279871689696093</v>
+        <v>0.04587659513437017</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.03621260870159226</v>
+        <v>0.02486303635544824</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.033333333333333</v>
       </c>
       <c r="AG15" t="n">
         <v>14</v>
       </c>
       <c r="AH15" t="n">
-        <v>89.96666666666667</v>
+        <v>90.06666666666666</v>
       </c>
       <c r="AI15" t="n">
-        <v>78.59580542074875</v>
+        <v>32.26423936150255</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.05132827627016434</v>
+        <v>0.02909716804684193</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.02646380849805441</v>
+        <v>0.01478746384877594</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.066666666666667</v>
+        <v>27.43333333333333</v>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
@@ -9031,115 +9031,115 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7.392996108949416</v>
+        <v>7.913043478260868</v>
       </c>
       <c r="C16" t="n">
-        <v>28.98832684824903</v>
+        <v>30.17391304347826</v>
       </c>
       <c r="D16" t="n">
-        <v>28.40466926070039</v>
+        <v>26</v>
       </c>
       <c r="E16" t="n">
-        <v>35.21400778210117</v>
+        <v>35.91304347826087</v>
       </c>
       <c r="F16" t="n">
-        <v>34.26666666666667</v>
+        <v>38.33333333333334</v>
       </c>
       <c r="G16" t="n">
-        <v>2.533333333333333</v>
+        <v>3.033333333333333</v>
       </c>
       <c r="H16" t="n">
-        <v>9.933333333333334</v>
+        <v>11.56666666666667</v>
       </c>
       <c r="I16" t="n">
-        <v>9.733333333333333</v>
+        <v>9.966666666666667</v>
       </c>
       <c r="J16" t="n">
-        <v>12.06666666666667</v>
+        <v>13.76666666666667</v>
       </c>
       <c r="K16" t="n">
-        <v>9.965706309323235</v>
+        <v>7.108874669803009</v>
       </c>
       <c r="L16" t="n">
-        <v>0.06841088359785126</v>
+        <v>0.04901885758490215</v>
       </c>
       <c r="M16" t="n">
-        <v>0.04237584418137645</v>
+        <v>0.02997965248345021</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.033333333333333</v>
       </c>
       <c r="O16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P16" t="n">
-        <v>116.3</v>
+        <v>115.5666666666667</v>
       </c>
       <c r="Q16" t="n">
-        <v>12.70045050145567</v>
+        <v>8.605897420133072</v>
       </c>
       <c r="R16" t="n">
-        <v>0.06825956387755855</v>
+        <v>0.05362558007027973</v>
       </c>
       <c r="S16" t="n">
-        <v>0.04641044679703543</v>
+        <v>0.03540619343877495</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>5.433333333333334</v>
       </c>
       <c r="U16" t="n">
         <v>14</v>
       </c>
       <c r="V16" t="n">
-        <v>130.5666666666667</v>
+        <v>130.5333333333333</v>
       </c>
       <c r="W16" t="n">
-        <v>10.34370898769007</v>
+        <v>6.168855830736188</v>
       </c>
       <c r="X16" t="n">
-        <v>0.05576266139438366</v>
+        <v>0.04375629390440973</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.05064496296632846</v>
+        <v>0.03753062157592487</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="AA16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB16" t="n">
-        <v>102.8333333333333</v>
+        <v>102.6666666666667</v>
       </c>
       <c r="AC16" t="n">
-        <v>29.5648064627782</v>
+        <v>9.741217240592093</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.03561349387572533</v>
+        <v>0.02302655437769945</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.02498234125510506</v>
+        <v>0.0159338292126027</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>10.56666666666667</v>
       </c>
       <c r="AG16" t="n">
         <v>13</v>
       </c>
       <c r="AH16" t="n">
-        <v>250.0666666666667</v>
+        <v>251.1666666666667</v>
       </c>
       <c r="AI16" t="n">
-        <v>68.01694432927081</v>
+        <v>34.78098466097251</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.05555055527543706</v>
+        <v>0.04007208933423584</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.03489683066992111</v>
+        <v>0.02433591192016049</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>20.26666666666667</v>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
@@ -9178,115 +9178,115 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18.08596918085969</v>
+        <v>17.67830045523521</v>
       </c>
       <c r="C17" t="n">
-        <v>13.13868613138686</v>
+        <v>13.05007587253414</v>
       </c>
       <c r="D17" t="n">
-        <v>20.92457420924574</v>
+        <v>22.45827010622155</v>
       </c>
       <c r="E17" t="n">
-        <v>47.85077047850771</v>
+        <v>46.81335356600911</v>
       </c>
       <c r="F17" t="n">
-        <v>41.1</v>
+        <v>43.93333333333333</v>
       </c>
       <c r="G17" t="n">
-        <v>7.433333333333334</v>
+        <v>7.766666666666667</v>
       </c>
       <c r="H17" t="n">
-        <v>5.4</v>
+        <v>5.733333333333333</v>
       </c>
       <c r="I17" t="n">
-        <v>8.6</v>
+        <v>9.866666666666667</v>
       </c>
       <c r="J17" t="n">
-        <v>19.66666666666667</v>
+        <v>20.56666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>13.10379062568351</v>
+        <v>8.970428720385286</v>
       </c>
       <c r="L17" t="n">
-        <v>0.06777879952473621</v>
+        <v>0.04633299084625721</v>
       </c>
       <c r="M17" t="n">
-        <v>0.04138178643230375</v>
+        <v>0.02638122864270383</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>8.566666666666666</v>
       </c>
       <c r="O17" t="n">
         <v>16</v>
       </c>
       <c r="P17" t="n">
-        <v>157</v>
+        <v>156.6333333333333</v>
       </c>
       <c r="Q17" t="n">
-        <v>8.775913774463385</v>
+        <v>5.686384912504613</v>
       </c>
       <c r="R17" t="n">
-        <v>0.06591821424067282</v>
+        <v>0.04853216698325425</v>
       </c>
       <c r="S17" t="n">
-        <v>0.04471196349215654</v>
+        <v>0.03371925800858524</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="U17" t="n">
         <v>16</v>
       </c>
       <c r="V17" t="n">
-        <v>116.3666666666667</v>
+        <v>116.5</v>
       </c>
       <c r="W17" t="n">
-        <v>43.9389851474932</v>
+        <v>11.42861574617886</v>
       </c>
       <c r="X17" t="n">
-        <v>0.05377787537202745</v>
+        <v>0.02579891120243098</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.04135493255770362</v>
+        <v>0.01746526090450858</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>18.86666666666667</v>
       </c>
       <c r="AA17" t="n">
         <v>15</v>
       </c>
       <c r="AB17" t="n">
-        <v>179.4</v>
+        <v>180</v>
       </c>
       <c r="AC17" t="n">
-        <v>14.42401382606931</v>
+        <v>6.310653218340605</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.05186985688549418</v>
+        <v>0.03431438294394386</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.03687986369607259</v>
+        <v>0.0246110643575926</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AG17" t="n">
         <v>13</v>
       </c>
       <c r="AH17" t="n">
-        <v>146.6</v>
+        <v>146.8333333333333</v>
       </c>
       <c r="AI17" t="n">
-        <v>85.91284075937787</v>
+        <v>36.85480033739518</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.05976401628594241</v>
+        <v>0.0374491615772371</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.03881410257435947</v>
+        <v>0.0220836758965165</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>37.13333333333333</v>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
@@ -9325,58 +9325,58 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14.82808022922636</v>
+        <v>14.72715318869165</v>
       </c>
       <c r="C18" t="n">
-        <v>24.06876790830946</v>
+        <v>23.53714661406969</v>
       </c>
       <c r="D18" t="n">
-        <v>25.64469914040114</v>
+        <v>24.19460880999343</v>
       </c>
       <c r="E18" t="n">
-        <v>35.45845272206304</v>
+        <v>37.54109138724523</v>
       </c>
       <c r="F18" t="n">
-        <v>46.53333333333333</v>
+        <v>50.7</v>
       </c>
       <c r="G18" t="n">
-        <v>6.9</v>
+        <v>7.466666666666667</v>
       </c>
       <c r="H18" t="n">
-        <v>11.2</v>
+        <v>11.93333333333333</v>
       </c>
       <c r="I18" t="n">
-        <v>11.93333333333333</v>
+        <v>12.26666666666667</v>
       </c>
       <c r="J18" t="n">
-        <v>16.5</v>
+        <v>19.03333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>20.50281456560725</v>
+        <v>8.541871516723685</v>
       </c>
       <c r="L18" t="n">
-        <v>0.06646710391942356</v>
+        <v>0.05152018660967481</v>
       </c>
       <c r="M18" t="n">
-        <v>0.05812005883324217</v>
+        <v>0.0334096391970426</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P18" t="n">
-        <v>135.3333333333333</v>
+        <v>133.5333333333333</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.827440780270052</v>
+        <v>5.10931202210995</v>
       </c>
       <c r="R18" t="n">
-        <v>0.04430467708374654</v>
+        <v>0.0371551230427364</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0487106042401173</v>
+        <v>0.024375738964713</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
@@ -9385,16 +9385,16 @@
         <v>11</v>
       </c>
       <c r="V18" t="n">
-        <v>111.8</v>
+        <v>112</v>
       </c>
       <c r="W18" t="n">
-        <v>9.284123361287961</v>
+        <v>6.387542795707033</v>
       </c>
       <c r="X18" t="n">
-        <v>0.08792790206671361</v>
+        <v>0.07531085869670313</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.05890364436432671</v>
+        <v>0.05172116174799637</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -9406,34 +9406,34 @@
         <v>76.36666666666666</v>
       </c>
       <c r="AC18" t="n">
-        <v>30.00117421291315</v>
+        <v>11.06271957572175</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.03633117433824302</v>
+        <v>0.02845273678149674</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.02725131067713343</v>
+        <v>0.01879647736670639</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.033333333333333</v>
+        <v>4.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AH18" t="n">
-        <v>274.8</v>
+        <v>278.0666666666667</v>
       </c>
       <c r="AI18" t="n">
-        <v>97.99418291519396</v>
+        <v>34.48713760977844</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.05170378292699662</v>
+        <v>0.04135178736170808</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.0319290282968131</v>
+        <v>0.02430879447760748</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.033333333333333</v>
+        <v>4.5</v>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
@@ -9472,40 +9472,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17.91208791208791</v>
+        <v>17.08378672470076</v>
       </c>
       <c r="C19" t="n">
-        <v>18.13186813186813</v>
+        <v>19.04243743199129</v>
       </c>
       <c r="D19" t="n">
-        <v>28.57142857142857</v>
+        <v>28.18280739934712</v>
       </c>
       <c r="E19" t="n">
-        <v>35.38461538461539</v>
+        <v>35.69096844396083</v>
       </c>
       <c r="F19" t="n">
-        <v>30.33333333333333</v>
+        <v>30.63333333333333</v>
       </c>
       <c r="G19" t="n">
-        <v>5.433333333333334</v>
+        <v>5.233333333333333</v>
       </c>
       <c r="H19" t="n">
-        <v>5.5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="I19" t="n">
-        <v>8.666666666666666</v>
+        <v>8.633333333333333</v>
       </c>
       <c r="J19" t="n">
-        <v>10.73333333333333</v>
+        <v>10.93333333333333</v>
       </c>
       <c r="K19" t="n">
-        <v>14.91498257776498</v>
+        <v>12.47138862195974</v>
       </c>
       <c r="L19" t="n">
-        <v>0.07997597438538603</v>
+        <v>0.07064773841488491</v>
       </c>
       <c r="M19" t="n">
-        <v>0.07006710729989463</v>
+        <v>0.05250294714689478</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -9514,16 +9514,16 @@
         <v>32</v>
       </c>
       <c r="P19" t="n">
-        <v>181.6333333333333</v>
+        <v>181.3666666666667</v>
       </c>
       <c r="Q19" t="n">
-        <v>13.05695439125836</v>
+        <v>8.825462621253056</v>
       </c>
       <c r="R19" t="n">
-        <v>0.07433873181734187</v>
+        <v>0.06751723959118429</v>
       </c>
       <c r="S19" t="n">
-        <v>0.04121500679076297</v>
+        <v>0.03598888177735145</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -9532,16 +9532,16 @@
         <v>30</v>
       </c>
       <c r="V19" t="n">
-        <v>133.7</v>
+        <v>133.6</v>
       </c>
       <c r="W19" t="n">
-        <v>7.229347173387797</v>
+        <v>5.647560966516272</v>
       </c>
       <c r="X19" t="n">
-        <v>0.05167501924353559</v>
+        <v>0.04335432998426716</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.04084459696614211</v>
+        <v>0.03703326919521371</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -9550,16 +9550,16 @@
         <v>25</v>
       </c>
       <c r="AB19" t="n">
-        <v>110</v>
+        <v>110.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>17.9184493419957</v>
+        <v>8.673262085996246</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.05115376734342061</v>
+        <v>0.04146578523161289</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.02678208655755603</v>
+        <v>0.02405546707489244</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -9568,16 +9568,16 @@
         <v>24</v>
       </c>
       <c r="AH19" t="n">
-        <v>174.3</v>
+        <v>174.6666666666667</v>
       </c>
       <c r="AI19" t="n">
-        <v>71.08223808062323</v>
+        <v>47.79149931744973</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.07365656338217688</v>
+        <v>0.06359829992561564</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.03559024092794483</v>
+        <v>0.03123381875687203</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -9619,61 +9619,61 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13.56553620531622</v>
+        <v>13.56693620844564</v>
       </c>
       <c r="C20" t="n">
-        <v>22.5481209899175</v>
+        <v>24.25876010781671</v>
       </c>
       <c r="D20" t="n">
-        <v>27.58936755270394</v>
+        <v>26.41509433962264</v>
       </c>
       <c r="E20" t="n">
-        <v>36.29697525206232</v>
+        <v>35.75920934411501</v>
       </c>
       <c r="F20" t="n">
-        <v>36.36666666666667</v>
+        <v>37.1</v>
       </c>
       <c r="G20" t="n">
-        <v>4.933333333333334</v>
+        <v>5.033333333333333</v>
       </c>
       <c r="H20" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="I20" t="n">
-        <v>10.03333333333333</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>13.2</v>
+        <v>13.26666666666667</v>
       </c>
       <c r="K20" t="n">
-        <v>12.98336924404003</v>
+        <v>8.693255734709679</v>
       </c>
       <c r="L20" t="n">
-        <v>0.05848885560998368</v>
+        <v>0.04062019993403297</v>
       </c>
       <c r="M20" t="n">
-        <v>0.02570745518655574</v>
+        <v>0.01580732943703048</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="O20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P20" t="n">
-        <v>196.4333333333333</v>
+        <v>196.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>8.329255435609326</v>
+        <v>4.520995940282161</v>
       </c>
       <c r="R20" t="n">
-        <v>0.04869837680482639</v>
+        <v>0.03751283646159835</v>
       </c>
       <c r="S20" t="n">
-        <v>0.03483858223186369</v>
+        <v>0.02586927774756032</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.033333333333333</v>
       </c>
       <c r="U20" t="n">
         <v>13</v>
@@ -9682,52 +9682,52 @@
         <v>99.63333333333334</v>
       </c>
       <c r="W20" t="n">
-        <v>15.7147894714663</v>
+        <v>8.902578707535534</v>
       </c>
       <c r="X20" t="n">
-        <v>0.05217716001477926</v>
+        <v>0.03356491865390714</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.024161867840319</v>
+        <v>0.01821011499734908</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>6.399999999999999</v>
       </c>
       <c r="AA20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AB20" t="n">
-        <v>205.3666666666667</v>
+        <v>205.5333333333333</v>
       </c>
       <c r="AC20" t="n">
-        <v>10.70071048008261</v>
+        <v>6.127666572893879</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.06512078122835029</v>
+        <v>0.0513161479825613</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.04899686038106855</v>
+        <v>0.04162080186332991</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="AG20" t="n">
         <v>14</v>
       </c>
       <c r="AH20" t="n">
-        <v>98.33333333333333</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AI20" t="n">
-        <v>53.87577870349017</v>
+        <v>32.9722456617719</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.05290225882181643</v>
+        <v>0.03613282557456707</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.02675524366384063</v>
+        <v>0.01995176000867172</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>10.73333333333333</v>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
@@ -9766,58 +9766,58 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19.65811965811966</v>
+        <v>21.17940199335548</v>
       </c>
       <c r="C21" t="n">
-        <v>42.64957264957265</v>
+        <v>35.96345514950166</v>
       </c>
       <c r="D21" t="n">
-        <v>22.73504273504274</v>
+        <v>25.33222591362126</v>
       </c>
       <c r="E21" t="n">
-        <v>14.95726495726496</v>
+        <v>17.5249169435216</v>
       </c>
       <c r="F21" t="n">
-        <v>39</v>
+        <v>40.13333333333333</v>
       </c>
       <c r="G21" t="n">
-        <v>7.666666666666667</v>
+        <v>8.5</v>
       </c>
       <c r="H21" t="n">
-        <v>16.63333333333333</v>
+        <v>14.43333333333333</v>
       </c>
       <c r="I21" t="n">
-        <v>8.866666666666667</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="J21" t="n">
-        <v>5.833333333333333</v>
+        <v>7.033333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>29.83468586750133</v>
+        <v>17.78711212896634</v>
       </c>
       <c r="L21" t="n">
-        <v>0.08434136269062341</v>
+        <v>0.05799496436675814</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1316501627699626</v>
+        <v>0.07880275779324165</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.466666666666667</v>
       </c>
       <c r="O21" t="n">
         <v>27</v>
       </c>
       <c r="P21" t="n">
-        <v>189.0333333333333</v>
+        <v>189.6333333333333</v>
       </c>
       <c r="Q21" t="n">
-        <v>12.48920136003267</v>
+        <v>8.877763207227758</v>
       </c>
       <c r="R21" t="n">
-        <v>0.05100310512188297</v>
+        <v>0.03833821933279453</v>
       </c>
       <c r="S21" t="n">
-        <v>0.03899452838799874</v>
+        <v>0.02721774671705119</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -9826,55 +9826,55 @@
         <v>30</v>
       </c>
       <c r="V21" t="n">
-        <v>187.3666666666667</v>
+        <v>187.7333333333333</v>
       </c>
       <c r="W21" t="n">
-        <v>10.61981509557088</v>
+        <v>6.305810010377304</v>
       </c>
       <c r="X21" t="n">
-        <v>0.1287415632800994</v>
+        <v>0.07671210220006289</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.07943508439984157</v>
+        <v>0.04412868241587068</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AB21" t="n">
-        <v>95.56666666666666</v>
+        <v>93.53333333333333</v>
       </c>
       <c r="AC21" t="n">
-        <v>32.04913002055646</v>
+        <v>12.75475766684485</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.2207184710784176</v>
+        <v>0.07879835019660912</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.2687385288549246</v>
+        <v>0.12112904910639</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AH21" t="n">
-        <v>127.8666666666667</v>
+        <v>129.0666666666667</v>
       </c>
       <c r="AI21" t="n">
-        <v>119.5637871215771</v>
+        <v>65.34403005752512</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.08846081611407419</v>
+        <v>0.06129810591586513</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.06496506130747803</v>
+        <v>0.04205120552683717</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>3.466666666666667</v>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
@@ -9913,115 +9913,115 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>18.29971181556196</v>
+        <v>16.41297154202515</v>
       </c>
       <c r="C22" t="n">
-        <v>29.82708933717579</v>
+        <v>27.39907346128392</v>
       </c>
       <c r="D22" t="n">
-        <v>16.4985590778098</v>
+        <v>22.8325612177366</v>
       </c>
       <c r="E22" t="n">
-        <v>35.37463976945245</v>
+        <v>33.35539377895434</v>
       </c>
       <c r="F22" t="n">
-        <v>46.26666666666667</v>
+        <v>50.36666666666667</v>
       </c>
       <c r="G22" t="n">
-        <v>8.466666666666667</v>
+        <v>8.266666666666667</v>
       </c>
       <c r="H22" t="n">
         <v>13.8</v>
       </c>
       <c r="I22" t="n">
-        <v>7.633333333333334</v>
+        <v>11.5</v>
       </c>
       <c r="J22" t="n">
-        <v>16.36666666666667</v>
+        <v>16.8</v>
       </c>
       <c r="K22" t="n">
-        <v>34.34373065933753</v>
+        <v>19.49936104172257</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1492923386024287</v>
+        <v>0.08908043784989775</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1574248894785186</v>
+        <v>0.07102758276035681</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P22" t="n">
-        <v>177.7666666666667</v>
+        <v>178.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>22.87706443027023</v>
+        <v>8.539600003604841</v>
       </c>
       <c r="R22" t="n">
-        <v>0.06188039955781864</v>
+        <v>0.0475446639597355</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0942340173289113</v>
+        <v>0.03216646878453272</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>4.233333333333333</v>
       </c>
       <c r="U22" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V22" t="n">
-        <v>150.5666666666667</v>
+        <v>150.8666666666667</v>
       </c>
       <c r="W22" t="n">
-        <v>25.92434516376629</v>
+        <v>11.40670066238647</v>
       </c>
       <c r="X22" t="n">
-        <v>0.1013567228709339</v>
+        <v>0.06152164868552919</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.1035496316175565</v>
+        <v>0.04568476468410884</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="AA22" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AB22" t="n">
-        <v>160.0666666666667</v>
+        <v>159.4333333333333</v>
       </c>
       <c r="AC22" t="n">
-        <v>13.34967878362108</v>
+        <v>7.458998749876171</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.09489453849944529</v>
+        <v>0.0611051843919345</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.1471713998381454</v>
+        <v>0.0607520472193977</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AH22" t="n">
-        <v>111</v>
+        <v>110.9333333333333</v>
       </c>
       <c r="AI22" t="n">
-        <v>118.2813273745831</v>
+        <v>60.02241781878731</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.1017919281763898</v>
+        <v>0.07454658502483552</v>
       </c>
       <c r="AK22" t="n">
-        <v>0.07075989565978091</v>
+        <v>0.04289759963967232</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
@@ -10060,58 +10060,58 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4.50281425891182</v>
+        <v>6.451612903225805</v>
       </c>
       <c r="C23" t="n">
-        <v>37.52345215759851</v>
+        <v>36.29032258064516</v>
       </c>
       <c r="D23" t="n">
-        <v>36.21013133208255</v>
+        <v>34.03225806451613</v>
       </c>
       <c r="E23" t="n">
-        <v>21.76360225140713</v>
+        <v>23.2258064516129</v>
       </c>
       <c r="F23" t="n">
-        <v>17.76666666666667</v>
+        <v>20.66666666666667</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="H23" t="n">
-        <v>6.666666666666667</v>
+        <v>7.5</v>
       </c>
       <c r="I23" t="n">
-        <v>6.433333333333334</v>
+        <v>7.033333333333333</v>
       </c>
       <c r="J23" t="n">
-        <v>3.866666666666667</v>
+        <v>4.8</v>
       </c>
       <c r="K23" t="n">
-        <v>12.62116018952886</v>
+        <v>11.24246614137915</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1115863098421371</v>
+        <v>0.1130846873892236</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1034914381750162</v>
+        <v>0.08754891913131571</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P23" t="n">
-        <v>207.2666666666667</v>
+        <v>207.9333333333333</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.589715141775526</v>
+        <v>2.158761765355997</v>
       </c>
       <c r="R23" t="n">
-        <v>0.09305571925272126</v>
+        <v>0.08782217359432795</v>
       </c>
       <c r="S23" t="n">
-        <v>0.06931723194859457</v>
+        <v>0.08900112579168579</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -10120,34 +10120,34 @@
         <v>80</v>
       </c>
       <c r="V23" t="n">
-        <v>110.5333333333333</v>
+        <v>109.6333333333333</v>
       </c>
       <c r="W23" t="n">
-        <v>9.634495416256906</v>
+        <v>6.828005648994639</v>
       </c>
       <c r="X23" t="n">
-        <v>0.1279210131519496</v>
+        <v>0.1087850365663902</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.1353783802734662</v>
+        <v>0.0735926741512378</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AB23" t="n">
-        <v>179.5</v>
+        <v>179.4333333333333</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.4547158517052028</v>
+        <v>0.4685583006254103</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.08367394874727174</v>
+        <v>0.0912734687710911</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.073886312406232</v>
+        <v>0.07109495279215661</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -10156,16 +10156,16 @@
         <v>84</v>
       </c>
       <c r="AH23" t="n">
-        <v>102.4</v>
+        <v>102.9333333333333</v>
       </c>
       <c r="AI23" t="n">
-        <v>130.1661801715097</v>
+        <v>109.867064162588</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.1771328718569804</v>
+        <v>0.1729069396975347</v>
       </c>
       <c r="AK23" t="n">
-        <v>0.09290993705648176</v>
+        <v>0.08602655222508604</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -10207,115 +10207,115 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>27.22335369993211</v>
+        <v>26.99811202013845</v>
       </c>
       <c r="C24" t="n">
-        <v>30.00678886625933</v>
+        <v>29.89301447451227</v>
       </c>
       <c r="D24" t="n">
-        <v>21.52070604209097</v>
+        <v>22.59282567652612</v>
       </c>
       <c r="E24" t="n">
-        <v>21.24915139171758</v>
+        <v>20.51604782882316</v>
       </c>
       <c r="F24" t="n">
-        <v>49.1</v>
+        <v>52.96666666666667</v>
       </c>
       <c r="G24" t="n">
-        <v>13.36666666666667</v>
+        <v>14.3</v>
       </c>
       <c r="H24" t="n">
-        <v>14.73333333333333</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="I24" t="n">
-        <v>10.56666666666667</v>
+        <v>11.96666666666667</v>
       </c>
       <c r="J24" t="n">
-        <v>10.43333333333333</v>
+        <v>10.86666666666667</v>
       </c>
       <c r="K24" t="n">
-        <v>13.80706812293346</v>
+        <v>11.76801243824387</v>
       </c>
       <c r="L24" t="n">
-        <v>0.05645983116987572</v>
+        <v>0.04836818490696495</v>
       </c>
       <c r="M24" t="n">
-        <v>0.03168993981986547</v>
+        <v>0.02684100390017537</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="O24" t="n">
         <v>25</v>
       </c>
       <c r="P24" t="n">
-        <v>201.5666666666667</v>
+        <v>201.8333333333333</v>
       </c>
       <c r="Q24" t="n">
-        <v>12.90354970001781</v>
+        <v>9.885232405986034</v>
       </c>
       <c r="R24" t="n">
-        <v>0.06865078847434558</v>
+        <v>0.05592063435875816</v>
       </c>
       <c r="S24" t="n">
-        <v>0.03732417013598541</v>
+        <v>0.03319227830070889</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="U24" t="n">
         <v>24</v>
       </c>
       <c r="V24" t="n">
-        <v>156.0333333333333</v>
+        <v>155.6</v>
       </c>
       <c r="W24" t="n">
-        <v>10.32953170382915</v>
+        <v>8.878210492047305</v>
       </c>
       <c r="X24" t="n">
-        <v>0.07113287327178611</v>
+        <v>0.06248014300394056</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.04328657611497921</v>
+        <v>0.04182449391247882</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AB24" t="n">
-        <v>131.7</v>
+        <v>131.5666666666667</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.76330887172864</v>
+        <v>7.21475303305802</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.06017697694299469</v>
+        <v>0.05585139331140968</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.03805650241816026</v>
+        <v>0.03809113522730923</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH24" t="n">
-        <v>110.6</v>
+        <v>110.9333333333333</v>
       </c>
       <c r="AI24" t="n">
-        <v>54.10050799588073</v>
+        <v>44.66288712485925</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.06854641636644077</v>
+        <v>0.06000380992507912</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.03599182979766136</v>
+        <v>0.03372264829263627</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>3.233333333333333</v>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
@@ -10354,115 +10354,115 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>14.51612903225807</v>
+        <v>14.91825613079019</v>
       </c>
       <c r="C25" t="n">
-        <v>22.58064516129032</v>
+        <v>23.29700272479564</v>
       </c>
       <c r="D25" t="n">
-        <v>38.00841514726508</v>
+        <v>37.12534059945504</v>
       </c>
       <c r="E25" t="n">
-        <v>24.89481065918654</v>
+        <v>24.65940054495913</v>
       </c>
       <c r="F25" t="n">
-        <v>47.53333333333333</v>
+        <v>48.93333333333333</v>
       </c>
       <c r="G25" t="n">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="H25" t="n">
-        <v>10.73333333333333</v>
+        <v>11.4</v>
       </c>
       <c r="I25" t="n">
-        <v>18.06666666666667</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="J25" t="n">
-        <v>11.83333333333333</v>
+        <v>12.06666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>19.19866130634958</v>
+        <v>11.03966167932657</v>
       </c>
       <c r="L25" t="n">
-        <v>0.08669658838141694</v>
+        <v>0.0703466590459787</v>
       </c>
       <c r="M25" t="n">
-        <v>0.08514658555902332</v>
+        <v>0.05759025735188396</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.033333333333333</v>
       </c>
       <c r="O25" t="n">
         <v>19</v>
       </c>
       <c r="P25" t="n">
-        <v>129.5</v>
+        <v>129.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>11.31835983621229</v>
+        <v>5.886556178621217</v>
       </c>
       <c r="R25" t="n">
-        <v>0.06445794633215003</v>
+        <v>0.05184419745073374</v>
       </c>
       <c r="S25" t="n">
-        <v>0.05492358493674167</v>
+        <v>0.04162569118566397</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="U25" t="n">
         <v>15</v>
       </c>
       <c r="V25" t="n">
-        <v>96.93333333333334</v>
+        <v>96.86666666666666</v>
       </c>
       <c r="W25" t="n">
-        <v>17.63308212105558</v>
+        <v>11.09039439064843</v>
       </c>
       <c r="X25" t="n">
-        <v>0.06522896246118225</v>
+        <v>0.04219250989900654</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.03738361865624579</v>
+        <v>0.0248490779413086</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB25" t="n">
-        <v>228.4666666666667</v>
+        <v>228.1666666666667</v>
       </c>
       <c r="AC25" t="n">
-        <v>14.44570293163464</v>
+        <v>7.268318716242781</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.05450510232469494</v>
+        <v>0.0373114947550352</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.05084682110205487</v>
+        <v>0.02597327544426747</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH25" t="n">
-        <v>144.8</v>
+        <v>145.1</v>
       </c>
       <c r="AI25" t="n">
-        <v>73.21681920032363</v>
+        <v>42.38842076050714</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.0643809411038189</v>
+        <v>0.04808443204204155</v>
       </c>
       <c r="AK25" t="n">
-        <v>0.03836196884032073</v>
+        <v>0.02824282199438344</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>16.2</v>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
